--- a/NoverojumuSkaits_wide_NoNo.xlsx
+++ b/NoverojumuSkaits_wide_NoNo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jekat\Desktop\HPC_jauns\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\taurinu_modeli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2B629B-7266-474B-BAFE-A01FD290AD81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33B01B3-B4BC-4BE6-9AA4-2FA7E6EE4F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1230" yWindow="1215" windowWidth="16860" windowHeight="12465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1590,7 +1588,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1600,12 +1598,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1655,17 +1647,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1964,12 +1955,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:P483"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="13" width="11.3828125" style="3"/>
+    <col min="1" max="16384" width="11.42578125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1997,20 +1988,20 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="2" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2038,12 +2029,8 @@
       <c r="I2">
         <v>116</v>
       </c>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-    </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2071,12 +2058,8 @@
       <c r="I3">
         <v>1130</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-    </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2104,12 +2087,8 @@
       <c r="I4">
         <v>53</v>
       </c>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-    </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2137,12 +2116,8 @@
       <c r="I5">
         <v>14</v>
       </c>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
-    </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2170,12 +2145,8 @@
       <c r="I6">
         <v>227</v>
       </c>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-    </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2203,12 +2174,8 @@
       <c r="I7">
         <v>322</v>
       </c>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-    </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2236,12 +2203,8 @@
       <c r="I8">
         <v>151</v>
       </c>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-    </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2269,12 +2232,8 @@
       <c r="I9">
         <v>1325</v>
       </c>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-    </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2302,12 +2261,8 @@
       <c r="I10">
         <v>571</v>
       </c>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-    </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2335,12 +2290,8 @@
       <c r="I11">
         <v>848</v>
       </c>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-    </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -2368,12 +2319,8 @@
       <c r="I12">
         <v>161</v>
       </c>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-    </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2401,12 +2348,8 @@
       <c r="I13">
         <v>20</v>
       </c>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2434,12 +2377,8 @@
       <c r="I14">
         <v>45</v>
       </c>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -2467,12 +2406,8 @@
       <c r="I15">
         <v>295</v>
       </c>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2500,12 +2435,8 @@
       <c r="I16">
         <v>53</v>
       </c>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-    </row>
-    <row r="17" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -2534,7 +2465,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -2563,7 +2494,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2592,7 +2523,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -2621,7 +2552,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -2650,7 +2581,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="22" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2679,7 +2610,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2708,7 +2639,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2737,7 +2668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2766,7 +2697,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="26" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2795,7 +2726,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -2824,7 +2755,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2853,7 +2784,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -2882,7 +2813,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -2911,7 +2842,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -2940,7 +2871,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -2969,7 +2900,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="33" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -2998,7 +2929,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -3027,7 +2958,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="35" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -3056,7 +2987,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="36" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -3085,7 +3016,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="37" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -3114,7 +3045,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -3143,7 +3074,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="39" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -3172,7 +3103,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="40" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -3201,7 +3132,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>24</v>
       </c>
@@ -3230,7 +3161,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="42" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -3259,7 +3190,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="43" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>24</v>
       </c>
@@ -3288,7 +3219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>24</v>
       </c>
@@ -3317,7 +3248,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -3346,7 +3277,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -3375,7 +3306,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -3404,7 +3335,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -3433,7 +3364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -3462,7 +3393,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -3491,7 +3422,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -3520,7 +3451,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -3549,7 +3480,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3578,7 +3509,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="54" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>24</v>
       </c>
@@ -3607,7 +3538,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>24</v>
       </c>
@@ -3636,7 +3567,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>24</v>
       </c>
@@ -3665,7 +3596,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -3694,7 +3625,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>24</v>
       </c>
@@ -3723,7 +3654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>24</v>
       </c>
@@ -3752,7 +3683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>24</v>
       </c>
@@ -3781,7 +3712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>24</v>
       </c>
@@ -3810,7 +3741,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -3839,7 +3770,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="63" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -3868,7 +3799,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>24</v>
       </c>
@@ -3897,7 +3828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>24</v>
       </c>
@@ -3926,7 +3857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -3955,7 +3886,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="67" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -3984,7 +3915,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="68" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -4013,7 +3944,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -4042,7 +3973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>78</v>
       </c>
@@ -4071,7 +4002,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="71" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -4100,7 +4031,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>78</v>
       </c>
@@ -4129,7 +4060,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="73" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -4158,7 +4089,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -4187,7 +4118,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -4216,7 +4147,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -4245,7 +4176,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="77" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -4274,7 +4205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -4303,7 +4234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -4332,7 +4263,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -4361,7 +4292,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="81" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>78</v>
       </c>
@@ -4390,7 +4321,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="82" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>78</v>
       </c>
@@ -4419,7 +4350,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>78</v>
       </c>
@@ -4448,7 +4379,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>78</v>
       </c>
@@ -4477,7 +4408,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="85" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>78</v>
       </c>
@@ -4506,7 +4437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -4535,7 +4466,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -4564,7 +4495,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -4593,7 +4524,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="89" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -4622,7 +4553,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -4651,7 +4582,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="91" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>97</v>
       </c>
@@ -4680,7 +4611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>97</v>
       </c>
@@ -4709,7 +4640,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="93" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -4738,7 +4669,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="94" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -4767,7 +4698,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="95" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -4796,7 +4727,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="96" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -4825,7 +4756,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -4854,7 +4785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -4883,7 +4814,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="99" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>97</v>
       </c>
@@ -4912,7 +4843,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="100" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>97</v>
       </c>
@@ -4941,7 +4872,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="101" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>97</v>
       </c>
@@ -4970,7 +4901,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="102" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -4999,7 +4930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>97</v>
       </c>
@@ -5028,7 +4959,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>97</v>
       </c>
@@ -5057,7 +4988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>97</v>
       </c>
@@ -5086,7 +5017,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="106" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>97</v>
       </c>
@@ -5115,7 +5046,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>97</v>
       </c>
@@ -5144,7 +5075,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>97</v>
       </c>
@@ -5173,7 +5104,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>97</v>
       </c>
@@ -5202,7 +5133,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>97</v>
       </c>
@@ -5231,7 +5162,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>97</v>
       </c>
@@ -5260,7 +5191,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="112" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>97</v>
       </c>
@@ -5289,7 +5220,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -5318,7 +5249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>97</v>
       </c>
@@ -5347,7 +5278,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="115" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>97</v>
       </c>
@@ -5376,7 +5307,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="116" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>97</v>
       </c>
@@ -5405,7 +5336,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>97</v>
       </c>
@@ -5434,7 +5365,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="118" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>97</v>
       </c>
@@ -5463,7 +5394,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="119" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>97</v>
       </c>
@@ -5492,7 +5423,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>97</v>
       </c>
@@ -5521,7 +5452,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="121" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>97</v>
       </c>
@@ -5550,7 +5481,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>97</v>
       </c>
@@ -5579,7 +5510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>97</v>
       </c>
@@ -5608,7 +5539,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="124" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>97</v>
       </c>
@@ -5637,7 +5568,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>97</v>
       </c>
@@ -5666,7 +5597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>97</v>
       </c>
@@ -5695,7 +5626,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="127" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>97</v>
       </c>
@@ -5724,7 +5655,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="128" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>140</v>
       </c>
@@ -5753,7 +5684,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="129" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>140</v>
       </c>
@@ -5782,7 +5713,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="130" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>140</v>
       </c>
@@ -5811,7 +5742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>140</v>
       </c>
@@ -5840,7 +5771,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="132" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>140</v>
       </c>
@@ -5869,7 +5800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="133" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -5898,7 +5829,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>147</v>
       </c>
@@ -5927,7 +5858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>147</v>
       </c>
@@ -5956,7 +5887,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>147</v>
       </c>
@@ -5985,7 +5916,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="137" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>147</v>
       </c>
@@ -6014,7 +5945,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="138" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>147</v>
       </c>
@@ -6043,7 +5974,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="139" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>147</v>
       </c>
@@ -6072,7 +6003,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="140" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>147</v>
       </c>
@@ -6101,7 +6032,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="141" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>147</v>
       </c>
@@ -6130,7 +6061,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="142" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>147</v>
       </c>
@@ -6159,7 +6090,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="143" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>147</v>
       </c>
@@ -6188,7 +6119,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="144" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>147</v>
       </c>
@@ -6217,7 +6148,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="145" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -6246,7 +6177,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="146" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>147</v>
       </c>
@@ -6275,7 +6206,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="147" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>147</v>
       </c>
@@ -6304,7 +6235,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="148" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>147</v>
       </c>
@@ -6333,7 +6264,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="149" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>147</v>
       </c>
@@ -6362,7 +6293,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>147</v>
       </c>
@@ -6391,7 +6322,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="151" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>147</v>
       </c>
@@ -6420,7 +6351,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>166</v>
       </c>
@@ -6449,7 +6380,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>166</v>
       </c>
@@ -6478,7 +6409,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="154" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>166</v>
       </c>
@@ -6507,7 +6438,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>166</v>
       </c>
@@ -6536,7 +6467,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>166</v>
       </c>
@@ -6565,7 +6496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>166</v>
       </c>
@@ -6594,7 +6525,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>166</v>
       </c>
@@ -6623,7 +6554,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="159" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -6652,7 +6583,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="160" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>166</v>
       </c>
@@ -6681,7 +6612,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="161" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>166</v>
       </c>
@@ -6710,7 +6641,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="162" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -6739,7 +6670,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="163" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>166</v>
       </c>
@@ -6768,7 +6699,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="164" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>179</v>
       </c>
@@ -6797,7 +6728,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>179</v>
       </c>
@@ -6826,7 +6757,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="166" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>179</v>
       </c>
@@ -6855,7 +6786,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="167" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>179</v>
       </c>
@@ -6884,7 +6815,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="168" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>184</v>
       </c>
@@ -6913,7 +6844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="169" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>184</v>
       </c>
@@ -6942,7 +6873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="170" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>184</v>
       </c>
@@ -6971,7 +6902,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="171" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>184</v>
       </c>
@@ -7000,7 +6931,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="172" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>184</v>
       </c>
@@ -7029,7 +6960,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>184</v>
       </c>
@@ -7058,7 +6989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>184</v>
       </c>
@@ -7087,7 +7018,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="175" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>184</v>
       </c>
@@ -7116,7 +7047,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>184</v>
       </c>
@@ -7145,7 +7076,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>184</v>
       </c>
@@ -7173,53 +7104,49 @@
       <c r="I177">
         <v>36</v>
       </c>
-      <c r="J177"/>
-      <c r="K177"/>
-      <c r="L177"/>
-      <c r="M177"/>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="1">
         <v>415</v>
       </c>
-      <c r="D178">
+      <c r="D178" s="1">
         <v>415</v>
       </c>
-      <c r="E178">
+      <c r="E178" s="1">
         <v>415</v>
       </c>
-      <c r="F178">
+      <c r="F178" s="1">
         <v>415</v>
       </c>
-      <c r="G178">
+      <c r="G178" s="1">
         <v>415</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="1">
         <v>405</v>
       </c>
-      <c r="I178">
+      <c r="I178" s="1">
         <v>377</v>
       </c>
-      <c r="J178" s="4">
+      <c r="J178" s="2">
         <v>0</v>
       </c>
-      <c r="K178" s="4">
+      <c r="K178" s="2">
         <v>0</v>
       </c>
-      <c r="L178" s="4">
+      <c r="L178" s="2">
         <v>1</v>
       </c>
-      <c r="M178" s="4">
+      <c r="M178" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>195</v>
       </c>
@@ -7247,12 +7174,12 @@
       <c r="I179">
         <v>125</v>
       </c>
-      <c r="J179" s="4"/>
-      <c r="K179" s="4"/>
-      <c r="L179" s="4"/>
-      <c r="M179" s="4"/>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J179" s="2"/>
+      <c r="K179" s="2"/>
+      <c r="L179" s="2"/>
+      <c r="M179" s="2"/>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>195</v>
       </c>
@@ -7280,12 +7207,12 @@
       <c r="I180">
         <v>85</v>
       </c>
-      <c r="J180" s="4"/>
-      <c r="K180" s="4"/>
-      <c r="L180" s="4"/>
-      <c r="M180" s="4"/>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J180" s="2"/>
+      <c r="K180" s="2"/>
+      <c r="L180" s="2"/>
+      <c r="M180" s="2"/>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>195</v>
       </c>
@@ -7313,12 +7240,12 @@
       <c r="I181">
         <v>152</v>
       </c>
-      <c r="J181" s="4"/>
-      <c r="K181" s="4"/>
-      <c r="L181" s="4"/>
-      <c r="M181" s="4"/>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J181" s="2"/>
+      <c r="K181" s="2"/>
+      <c r="L181" s="2"/>
+      <c r="M181" s="2"/>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>195</v>
       </c>
@@ -7346,12 +7273,12 @@
       <c r="I182">
         <v>115</v>
       </c>
-      <c r="J182" s="4"/>
-      <c r="K182" s="4"/>
-      <c r="L182" s="4"/>
-      <c r="M182" s="4"/>
-    </row>
-    <row r="183" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="J182" s="2"/>
+      <c r="K182" s="2"/>
+      <c r="L182" s="2"/>
+      <c r="M182" s="2"/>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>195</v>
       </c>
@@ -7379,20 +7306,20 @@
       <c r="I183" s="1">
         <v>658</v>
       </c>
-      <c r="J183" s="4">
+      <c r="J183" s="2">
         <v>0</v>
       </c>
-      <c r="K183" s="4">
+      <c r="K183" s="2">
         <v>0</v>
       </c>
-      <c r="L183" s="5">
+      <c r="L183" s="3">
         <v>1</v>
       </c>
-      <c r="M183" s="9">
+      <c r="M183" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>195</v>
       </c>
@@ -7420,144 +7347,176 @@
       <c r="I184">
         <v>46</v>
       </c>
-      <c r="J184" s="4"/>
-      <c r="K184" s="4"/>
-      <c r="L184" s="4"/>
-      <c r="M184" s="4"/>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J184" s="2"/>
+      <c r="K184" s="2"/>
+      <c r="L184" s="2"/>
+      <c r="M184" s="2"/>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="1">
         <v>234</v>
       </c>
-      <c r="D185">
+      <c r="D185" s="1">
         <v>234</v>
       </c>
-      <c r="E185">
+      <c r="E185" s="1">
         <v>232</v>
       </c>
-      <c r="F185">
+      <c r="F185" s="1">
         <v>232</v>
       </c>
-      <c r="G185">
+      <c r="G185" s="1">
         <v>232</v>
       </c>
-      <c r="H185">
+      <c r="H185" s="1">
         <v>210</v>
       </c>
-      <c r="I185">
+      <c r="I185" s="1">
         <v>172</v>
       </c>
-      <c r="J185" s="4"/>
-      <c r="K185" s="4"/>
-      <c r="L185" s="4"/>
-      <c r="M185" s="4"/>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J185" s="2">
+        <v>0</v>
+      </c>
+      <c r="K185" s="2">
+        <v>0</v>
+      </c>
+      <c r="L185" s="2">
+        <v>1</v>
+      </c>
+      <c r="M185" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="1">
         <v>331</v>
       </c>
-      <c r="D186">
+      <c r="D186" s="1">
         <v>331</v>
       </c>
-      <c r="E186">
+      <c r="E186" s="1">
         <v>331</v>
       </c>
-      <c r="F186">
+      <c r="F186" s="1">
         <v>331</v>
       </c>
-      <c r="G186">
+      <c r="G186" s="1">
         <v>331</v>
       </c>
-      <c r="H186">
+      <c r="H186" s="1">
         <v>325</v>
       </c>
-      <c r="I186">
+      <c r="I186" s="1">
         <v>293</v>
       </c>
-      <c r="J186" s="4"/>
-      <c r="K186" s="4"/>
-      <c r="L186" s="4"/>
-      <c r="M186" s="4"/>
-    </row>
-    <row r="187" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="2" t="s">
+      <c r="J186" s="2">
+        <v>0</v>
+      </c>
+      <c r="K186" s="2">
+        <v>0</v>
+      </c>
+      <c r="L186" s="2">
+        <v>1</v>
+      </c>
+      <c r="M186" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A187" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B187" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C187" s="2">
+      <c r="C187" s="8">
         <v>45</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="8">
         <v>45</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="8">
         <v>45</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="8">
         <v>45</v>
       </c>
-      <c r="G187" s="2">
+      <c r="G187" s="8">
         <v>45</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="8">
         <v>41</v>
       </c>
-      <c r="I187" s="2">
+      <c r="I187" s="8">
         <v>29</v>
       </c>
-      <c r="J187" s="4"/>
-      <c r="K187" s="4"/>
-      <c r="L187" s="4"/>
-      <c r="M187" s="4"/>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J187" s="2">
+        <v>1</v>
+      </c>
+      <c r="K187" s="2">
+        <v>0</v>
+      </c>
+      <c r="L187" s="3">
+        <v>1</v>
+      </c>
+      <c r="M187" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C188">
+      <c r="C188" s="1">
         <v>88</v>
       </c>
-      <c r="D188">
+      <c r="D188" s="1">
         <v>88</v>
       </c>
-      <c r="E188">
+      <c r="E188" s="1">
         <v>88</v>
       </c>
-      <c r="F188">
+      <c r="F188" s="1">
         <v>88</v>
       </c>
-      <c r="G188">
+      <c r="G188" s="1">
         <v>88</v>
       </c>
-      <c r="H188">
+      <c r="H188" s="1">
         <v>74</v>
       </c>
-      <c r="I188">
+      <c r="I188" s="1">
         <v>60</v>
       </c>
-      <c r="J188" s="4"/>
-      <c r="K188" s="4"/>
-      <c r="L188" s="4"/>
-      <c r="M188" s="4"/>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J188" s="2">
+        <v>0</v>
+      </c>
+      <c r="K188" s="2">
+        <v>0</v>
+      </c>
+      <c r="L188" s="2">
+        <v>1</v>
+      </c>
+      <c r="M188" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>195</v>
       </c>
@@ -7585,12 +7544,12 @@
       <c r="I189">
         <v>164</v>
       </c>
-      <c r="J189" s="4"/>
-      <c r="K189" s="4"/>
-      <c r="L189" s="4"/>
-      <c r="M189" s="4"/>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J189" s="2"/>
+      <c r="K189" s="2"/>
+      <c r="L189" s="2"/>
+      <c r="M189" s="2"/>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>195</v>
       </c>
@@ -7618,12 +7577,12 @@
       <c r="I190">
         <v>0</v>
       </c>
-      <c r="J190" s="4"/>
-      <c r="K190" s="4"/>
-      <c r="L190" s="4"/>
-      <c r="M190" s="4"/>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J190" s="2"/>
+      <c r="K190" s="2"/>
+      <c r="L190" s="2"/>
+      <c r="M190" s="2"/>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>195</v>
       </c>
@@ -7651,16 +7610,16 @@
       <c r="I191">
         <v>177</v>
       </c>
-      <c r="J191" s="4"/>
-      <c r="K191" s="4"/>
-      <c r="L191" s="4"/>
-      <c r="M191" s="4"/>
-      <c r="O191" s="7"/>
-      <c r="P191" t="s">
+      <c r="J191" s="2"/>
+      <c r="K191" s="2"/>
+      <c r="L191" s="2"/>
+      <c r="M191" s="2"/>
+      <c r="O191" s="5"/>
+      <c r="P191" s="8" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>195</v>
       </c>
@@ -7688,86 +7647,102 @@
       <c r="I192">
         <v>237</v>
       </c>
-      <c r="J192" s="4"/>
-      <c r="K192" s="4"/>
-      <c r="L192" s="4"/>
-      <c r="M192" s="4"/>
-      <c r="O192" s="6"/>
-      <c r="P192" t="s">
+      <c r="J192" s="2"/>
+      <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
+      <c r="M192" s="2"/>
+      <c r="O192" s="4"/>
+      <c r="P192" s="8" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C193">
+      <c r="C193" s="1">
         <v>587</v>
       </c>
-      <c r="D193">
+      <c r="D193" s="1">
         <v>587</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="1">
         <v>587</v>
       </c>
-      <c r="F193">
+      <c r="F193" s="1">
         <v>587</v>
       </c>
-      <c r="G193">
+      <c r="G193" s="1">
         <v>587</v>
       </c>
-      <c r="H193">
+      <c r="H193" s="1">
         <v>539</v>
       </c>
-      <c r="I193">
+      <c r="I193" s="1">
         <v>419</v>
       </c>
-      <c r="J193" s="4"/>
-      <c r="K193" s="4"/>
-      <c r="L193" s="4"/>
-      <c r="M193" s="4"/>
-      <c r="O193" s="8"/>
-      <c r="P193" t="s">
+      <c r="J193" s="2">
+        <v>0</v>
+      </c>
+      <c r="K193" s="2">
+        <v>0</v>
+      </c>
+      <c r="L193" s="2">
+        <v>1</v>
+      </c>
+      <c r="M193" s="2">
+        <v>1</v>
+      </c>
+      <c r="O193" s="6"/>
+      <c r="P193" s="8" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="1">
         <v>796</v>
       </c>
-      <c r="D194">
+      <c r="D194" s="1">
         <v>796</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="1">
         <v>796</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="1">
         <v>796</v>
       </c>
-      <c r="G194">
+      <c r="G194" s="1">
         <v>796</v>
       </c>
-      <c r="H194">
+      <c r="H194" s="1">
         <v>734</v>
       </c>
-      <c r="I194">
+      <c r="I194" s="1">
         <v>604</v>
       </c>
-      <c r="J194" s="4"/>
-      <c r="K194" s="4"/>
-      <c r="L194" s="4"/>
-      <c r="M194" s="4"/>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J194" s="2">
+        <v>0</v>
+      </c>
+      <c r="K194" s="2">
+        <v>0</v>
+      </c>
+      <c r="L194" s="2">
+        <v>1</v>
+      </c>
+      <c r="M194" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>195</v>
       </c>
@@ -7795,45 +7770,53 @@
       <c r="I195">
         <v>133</v>
       </c>
-      <c r="J195" s="4"/>
-      <c r="K195" s="4"/>
-      <c r="L195" s="4"/>
-      <c r="M195" s="4"/>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J195" s="2"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2"/>
+      <c r="M195" s="2"/>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="1">
         <v>977</v>
       </c>
-      <c r="D196">
+      <c r="D196" s="1">
         <v>977</v>
       </c>
-      <c r="E196">
+      <c r="E196" s="1">
         <v>977</v>
       </c>
-      <c r="F196">
+      <c r="F196" s="1">
         <v>977</v>
       </c>
-      <c r="G196">
+      <c r="G196" s="1">
         <v>977</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="1">
         <v>916</v>
       </c>
-      <c r="I196">
+      <c r="I196" s="1">
         <v>743</v>
       </c>
-      <c r="J196" s="4"/>
-      <c r="K196" s="4"/>
-      <c r="L196" s="4"/>
-      <c r="M196" s="4"/>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J196" s="2">
+        <v>0</v>
+      </c>
+      <c r="K196" s="2">
+        <v>0</v>
+      </c>
+      <c r="L196" s="2">
+        <v>1</v>
+      </c>
+      <c r="M196" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>195</v>
       </c>
@@ -7861,12 +7844,20 @@
       <c r="I197">
         <v>405</v>
       </c>
-      <c r="J197" s="4"/>
-      <c r="K197" s="4"/>
-      <c r="L197" s="4"/>
-      <c r="M197" s="4"/>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J197" s="2">
+        <v>0</v>
+      </c>
+      <c r="K197" s="2">
+        <v>0</v>
+      </c>
+      <c r="L197" s="2">
+        <v>1</v>
+      </c>
+      <c r="M197" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>195</v>
       </c>
@@ -7894,12 +7885,12 @@
       <c r="I198">
         <v>117</v>
       </c>
-      <c r="J198" s="4"/>
-      <c r="K198" s="4"/>
-      <c r="L198" s="4"/>
-      <c r="M198" s="4"/>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J198" s="2"/>
+      <c r="K198" s="2"/>
+      <c r="L198" s="2"/>
+      <c r="M198" s="2"/>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>195</v>
       </c>
@@ -7927,12 +7918,12 @@
       <c r="I199">
         <v>575</v>
       </c>
-      <c r="J199" s="4"/>
-      <c r="K199" s="4"/>
-      <c r="L199" s="4"/>
-      <c r="M199" s="4"/>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="J199" s="2"/>
+      <c r="K199" s="2"/>
+      <c r="L199" s="2"/>
+      <c r="M199" s="2"/>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>195</v>
       </c>
@@ -7960,12 +7951,12 @@
       <c r="I200">
         <v>52</v>
       </c>
-      <c r="J200" s="4"/>
-      <c r="K200" s="4"/>
-      <c r="L200" s="4"/>
-      <c r="M200" s="4"/>
-    </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+      <c r="J200" s="2"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
+      <c r="M200" s="2"/>
+    </row>
+    <row r="201" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>219</v>
       </c>
@@ -7993,12 +7984,8 @@
       <c r="I201">
         <v>102</v>
       </c>
-      <c r="J201"/>
-      <c r="K201"/>
-      <c r="L201"/>
-      <c r="M201"/>
-    </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="202" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>219</v>
       </c>
@@ -8026,12 +8013,8 @@
       <c r="I202">
         <v>46</v>
       </c>
-      <c r="J202"/>
-      <c r="K202"/>
-      <c r="L202"/>
-      <c r="M202"/>
-    </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="203" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>219</v>
       </c>
@@ -8059,12 +8042,8 @@
       <c r="I203">
         <v>67</v>
       </c>
-      <c r="J203"/>
-      <c r="K203"/>
-      <c r="L203"/>
-      <c r="M203"/>
-    </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="204" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>219</v>
       </c>
@@ -8092,12 +8071,8 @@
       <c r="I204">
         <v>63</v>
       </c>
-      <c r="J204"/>
-      <c r="K204"/>
-      <c r="L204"/>
-      <c r="M204"/>
-    </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="205" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>219</v>
       </c>
@@ -8125,12 +8100,8 @@
       <c r="I205">
         <v>153</v>
       </c>
-      <c r="J205"/>
-      <c r="K205"/>
-      <c r="L205"/>
-      <c r="M205"/>
-    </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="206" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>219</v>
       </c>
@@ -8158,12 +8129,8 @@
       <c r="I206">
         <v>58</v>
       </c>
-      <c r="J206"/>
-      <c r="K206"/>
-      <c r="L206"/>
-      <c r="M206"/>
-    </row>
-    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="207" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>219</v>
       </c>
@@ -8191,12 +8158,8 @@
       <c r="I207">
         <v>94</v>
       </c>
-      <c r="J207"/>
-      <c r="K207"/>
-      <c r="L207"/>
-      <c r="M207"/>
-    </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="208" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>219</v>
       </c>
@@ -8224,12 +8187,8 @@
       <c r="I208">
         <v>184</v>
       </c>
-      <c r="J208"/>
-      <c r="K208"/>
-      <c r="L208"/>
-      <c r="M208"/>
-    </row>
-    <row r="209" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="209" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>219</v>
       </c>
@@ -8258,7 +8217,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="210" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>219</v>
       </c>
@@ -8287,7 +8246,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="211" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>230</v>
       </c>
@@ -8316,7 +8275,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="212" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>230</v>
       </c>
@@ -8345,7 +8304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>230</v>
       </c>
@@ -8374,7 +8333,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="214" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>230</v>
       </c>
@@ -8403,7 +8362,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="215" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>230</v>
       </c>
@@ -8432,7 +8391,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="216" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>230</v>
       </c>
@@ -8461,7 +8420,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="217" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>237</v>
       </c>
@@ -8490,7 +8449,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="218" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>237</v>
       </c>
@@ -8519,7 +8478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>237</v>
       </c>
@@ -8548,7 +8507,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="220" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>237</v>
       </c>
@@ -8577,7 +8536,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="221" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>237</v>
       </c>
@@ -8606,7 +8565,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="222" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>237</v>
       </c>
@@ -8635,7 +8594,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="223" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>237</v>
       </c>
@@ -8664,7 +8623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>237</v>
       </c>
@@ -8693,7 +8652,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="225" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>237</v>
       </c>
@@ -8722,7 +8681,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>237</v>
       </c>
@@ -8751,7 +8710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>237</v>
       </c>
@@ -8780,7 +8739,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="228" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>237</v>
       </c>
@@ -8809,7 +8768,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="229" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>237</v>
       </c>
@@ -8838,7 +8797,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="230" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>237</v>
       </c>
@@ -8867,7 +8826,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="231" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>237</v>
       </c>
@@ -8896,7 +8855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>237</v>
       </c>
@@ -8925,7 +8884,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="233" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>237</v>
       </c>
@@ -8954,7 +8913,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="234" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>237</v>
       </c>
@@ -8983,7 +8942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>237</v>
       </c>
@@ -9012,7 +8971,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="236" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>237</v>
       </c>
@@ -9041,7 +9000,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="237" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>237</v>
       </c>
@@ -9070,7 +9029,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="238" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>237</v>
       </c>
@@ -9099,7 +9058,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>237</v>
       </c>
@@ -9128,7 +9087,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="240" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>237</v>
       </c>
@@ -9157,7 +9116,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="241" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>237</v>
       </c>
@@ -9186,7 +9145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>237</v>
       </c>
@@ -9215,7 +9174,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="243" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>237</v>
       </c>
@@ -9244,7 +9203,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="244" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>237</v>
       </c>
@@ -9273,7 +9232,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="245" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>237</v>
       </c>
@@ -9302,7 +9261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>237</v>
       </c>
@@ -9331,7 +9290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>237</v>
       </c>
@@ -9360,7 +9319,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="248" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>237</v>
       </c>
@@ -9389,7 +9348,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="249" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>237</v>
       </c>
@@ -9418,7 +9377,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="250" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>237</v>
       </c>
@@ -9447,7 +9406,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="251" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>237</v>
       </c>
@@ -9476,7 +9435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="252" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>237</v>
       </c>
@@ -9505,7 +9464,7 @@
         <v>4038</v>
       </c>
     </row>
-    <row r="253" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>237</v>
       </c>
@@ -9534,7 +9493,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>237</v>
       </c>
@@ -9563,7 +9522,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="255" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>237</v>
       </c>
@@ -9592,7 +9551,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="256" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>237</v>
       </c>
@@ -9621,7 +9580,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="257" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>237</v>
       </c>
@@ -9650,7 +9609,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="258" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>237</v>
       </c>
@@ -9679,7 +9638,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="259" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>237</v>
       </c>
@@ -9708,7 +9667,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="260" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>237</v>
       </c>
@@ -9737,7 +9696,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="261" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>237</v>
       </c>
@@ -9766,7 +9725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>237</v>
       </c>
@@ -9795,7 +9754,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="263" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>237</v>
       </c>
@@ -9824,7 +9783,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>237</v>
       </c>
@@ -9853,7 +9812,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="265" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>237</v>
       </c>
@@ -9882,7 +9841,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="266" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>237</v>
       </c>
@@ -9911,7 +9870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>237</v>
       </c>
@@ -9940,7 +9899,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="268" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>237</v>
       </c>
@@ -9969,7 +9928,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="269" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>237</v>
       </c>
@@ -9998,7 +9957,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="270" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>237</v>
       </c>
@@ -10027,7 +9986,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="271" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>237</v>
       </c>
@@ -10056,7 +10015,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="272" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>237</v>
       </c>
@@ -10085,7 +10044,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="273" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>237</v>
       </c>
@@ -10114,7 +10073,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="274" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>237</v>
       </c>
@@ -10143,7 +10102,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="275" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>237</v>
       </c>
@@ -10172,7 +10131,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="276" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>237</v>
       </c>
@@ -10201,7 +10160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="277" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>237</v>
       </c>
@@ -10230,7 +10189,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>237</v>
       </c>
@@ -10259,7 +10218,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>237</v>
       </c>
@@ -10288,7 +10247,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="280" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>237</v>
       </c>
@@ -10317,7 +10276,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="281" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>237</v>
       </c>
@@ -10346,7 +10305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="282" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>237</v>
       </c>
@@ -10375,7 +10334,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>237</v>
       </c>
@@ -10404,7 +10363,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="284" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>237</v>
       </c>
@@ -10433,7 +10392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="285" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>237</v>
       </c>
@@ -10462,7 +10421,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="286" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>237</v>
       </c>
@@ -10491,7 +10450,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="287" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>237</v>
       </c>
@@ -10520,7 +10479,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="288" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>237</v>
       </c>
@@ -10549,7 +10508,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="289" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>237</v>
       </c>
@@ -10578,7 +10537,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="290" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>237</v>
       </c>
@@ -10607,7 +10566,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="291" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>237</v>
       </c>
@@ -10636,7 +10595,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="292" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>237</v>
       </c>
@@ -10665,7 +10624,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="293" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>237</v>
       </c>
@@ -10694,7 +10653,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="294" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>237</v>
       </c>
@@ -10723,7 +10682,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="295" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>237</v>
       </c>
@@ -10752,7 +10711,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="296" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>237</v>
       </c>
@@ -10781,7 +10740,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="297" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>237</v>
       </c>
@@ -10810,7 +10769,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="298" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>237</v>
       </c>
@@ -10839,7 +10798,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="299" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>237</v>
       </c>
@@ -10868,7 +10827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>237</v>
       </c>
@@ -10897,7 +10856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>237</v>
       </c>
@@ -10926,7 +10885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="302" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>237</v>
       </c>
@@ -10955,7 +10914,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="303" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>237</v>
       </c>
@@ -10984,7 +10943,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="304" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>237</v>
       </c>
@@ -11013,7 +10972,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="305" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>237</v>
       </c>
@@ -11042,7 +11001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="306" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>237</v>
       </c>
@@ -11071,7 +11030,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="307" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>237</v>
       </c>
@@ -11100,7 +11059,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="308" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>237</v>
       </c>
@@ -11129,7 +11088,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="309" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>237</v>
       </c>
@@ -11158,7 +11117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>237</v>
       </c>
@@ -11187,7 +11146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="311" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>237</v>
       </c>
@@ -11216,7 +11175,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="312" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>237</v>
       </c>
@@ -11245,7 +11204,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="313" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>237</v>
       </c>
@@ -11274,7 +11233,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="314" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>237</v>
       </c>
@@ -11303,7 +11262,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="315" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>237</v>
       </c>
@@ -11332,7 +11291,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="316" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>237</v>
       </c>
@@ -11361,7 +11320,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="317" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>237</v>
       </c>
@@ -11390,7 +11349,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="318" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>237</v>
       </c>
@@ -11419,7 +11378,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="319" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>237</v>
       </c>
@@ -11448,7 +11407,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>237</v>
       </c>
@@ -11477,7 +11436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="321" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>237</v>
       </c>
@@ -11506,7 +11465,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="322" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>237</v>
       </c>
@@ -11535,7 +11494,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="323" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>237</v>
       </c>
@@ -11564,7 +11523,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="324" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>237</v>
       </c>
@@ -11593,7 +11552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>237</v>
       </c>
@@ -11622,7 +11581,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="326" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>237</v>
       </c>
@@ -11651,7 +11610,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="327" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>237</v>
       </c>
@@ -11680,7 +11639,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="328" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>237</v>
       </c>
@@ -11709,7 +11668,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="329" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>237</v>
       </c>
@@ -11738,7 +11697,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="330" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>237</v>
       </c>
@@ -11767,7 +11726,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="331" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>237</v>
       </c>
@@ -11796,7 +11755,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="332" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>237</v>
       </c>
@@ -11825,7 +11784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="333" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>237</v>
       </c>
@@ -11854,7 +11813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="334" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>237</v>
       </c>
@@ -11883,7 +11842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="335" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>237</v>
       </c>
@@ -11912,7 +11871,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="336" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>237</v>
       </c>
@@ -11941,7 +11900,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="337" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>237</v>
       </c>
@@ -11970,7 +11929,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="338" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>237</v>
       </c>
@@ -11999,7 +11958,7 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="339" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>237</v>
       </c>
@@ -12028,7 +11987,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="340" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>237</v>
       </c>
@@ -12057,7 +12016,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="341" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>237</v>
       </c>
@@ -12086,7 +12045,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="342" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>237</v>
       </c>
@@ -12115,7 +12074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>237</v>
       </c>
@@ -12144,7 +12103,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="344" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>237</v>
       </c>
@@ -12173,7 +12132,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="345" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>237</v>
       </c>
@@ -12202,7 +12161,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="346" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>237</v>
       </c>
@@ -12231,7 +12190,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="347" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>237</v>
       </c>
@@ -12260,7 +12219,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="348" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>237</v>
       </c>
@@ -12289,7 +12248,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="349" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>237</v>
       </c>
@@ -12318,7 +12277,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="350" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>237</v>
       </c>
@@ -12347,7 +12306,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="351" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>237</v>
       </c>
@@ -12376,7 +12335,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="352" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>237</v>
       </c>
@@ -12405,7 +12364,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="353" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>237</v>
       </c>
@@ -12434,7 +12393,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="354" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>237</v>
       </c>
@@ -12463,7 +12422,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="355" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>237</v>
       </c>
@@ -12492,7 +12451,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="356" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>237</v>
       </c>
@@ -12521,7 +12480,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="357" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>237</v>
       </c>
@@ -12550,7 +12509,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="358" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>237</v>
       </c>
@@ -12579,7 +12538,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="359" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>237</v>
       </c>
@@ -12608,7 +12567,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="360" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>237</v>
       </c>
@@ -12637,7 +12596,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="361" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>237</v>
       </c>
@@ -12666,7 +12625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>237</v>
       </c>
@@ -12695,7 +12654,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="363" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>237</v>
       </c>
@@ -12724,7 +12683,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="364" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>237</v>
       </c>
@@ -12753,7 +12712,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="365" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>237</v>
       </c>
@@ -12782,7 +12741,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="366" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>237</v>
       </c>
@@ -12811,7 +12770,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="367" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>237</v>
       </c>
@@ -12840,7 +12799,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="368" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>237</v>
       </c>
@@ -12869,7 +12828,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="369" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>237</v>
       </c>
@@ -12898,7 +12857,7 @@
         <v>4853</v>
       </c>
     </row>
-    <row r="370" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>237</v>
       </c>
@@ -12927,7 +12886,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="371" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>237</v>
       </c>
@@ -12956,7 +12915,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="372" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>237</v>
       </c>
@@ -12985,7 +12944,7 @@
         <v>3360</v>
       </c>
     </row>
-    <row r="373" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>237</v>
       </c>
@@ -13014,7 +12973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>237</v>
       </c>
@@ -13043,7 +13002,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="375" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>237</v>
       </c>
@@ -13072,7 +13031,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="376" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>237</v>
       </c>
@@ -13101,7 +13060,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="377" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>237</v>
       </c>
@@ -13130,7 +13089,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="378" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>237</v>
       </c>
@@ -13159,7 +13118,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="379" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>237</v>
       </c>
@@ -13188,7 +13147,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="380" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>237</v>
       </c>
@@ -13217,7 +13176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="381" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>237</v>
       </c>
@@ -13246,7 +13205,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="382" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>237</v>
       </c>
@@ -13275,7 +13234,7 @@
         <v>4339</v>
       </c>
     </row>
-    <row r="383" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>237</v>
       </c>
@@ -13304,7 +13263,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="384" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>237</v>
       </c>
@@ -13333,7 +13292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="385" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>237</v>
       </c>
@@ -13362,7 +13321,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="386" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>237</v>
       </c>
@@ -13391,7 +13350,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="387" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>237</v>
       </c>
@@ -13420,7 +13379,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="388" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>237</v>
       </c>
@@ -13449,7 +13408,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="389" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>237</v>
       </c>
@@ -13478,7 +13437,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="390" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>237</v>
       </c>
@@ -13507,7 +13466,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="391" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>237</v>
       </c>
@@ -13536,7 +13495,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="392" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>237</v>
       </c>
@@ -13565,7 +13524,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="393" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>237</v>
       </c>
@@ -13594,7 +13553,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="394" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>237</v>
       </c>
@@ -13623,7 +13582,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="395" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>237</v>
       </c>
@@ -13652,7 +13611,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="396" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>237</v>
       </c>
@@ -13681,7 +13640,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="397" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>237</v>
       </c>
@@ -13710,7 +13669,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="398" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>237</v>
       </c>
@@ -13739,7 +13698,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="399" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>237</v>
       </c>
@@ -13768,7 +13727,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="400" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>237</v>
       </c>
@@ -13797,7 +13756,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="401" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>237</v>
       </c>
@@ -13826,7 +13785,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="402" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>237</v>
       </c>
@@ -13855,7 +13814,7 @@
         <v>2563</v>
       </c>
     </row>
-    <row r="403" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>237</v>
       </c>
@@ -13884,7 +13843,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="404" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>237</v>
       </c>
@@ -13913,7 +13872,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="405" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>237</v>
       </c>
@@ -13942,7 +13901,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="406" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>237</v>
       </c>
@@ -13971,7 +13930,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="407" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>237</v>
       </c>
@@ -14000,7 +13959,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="408" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>237</v>
       </c>
@@ -14029,7 +13988,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="409" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>237</v>
       </c>
@@ -14058,7 +14017,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="410" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>237</v>
       </c>
@@ -14087,7 +14046,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="411" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>237</v>
       </c>
@@ -14116,7 +14075,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="412" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>237</v>
       </c>
@@ -14145,7 +14104,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="413" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>237</v>
       </c>
@@ -14174,7 +14133,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="414" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>237</v>
       </c>
@@ -14203,7 +14162,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="415" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>237</v>
       </c>
@@ -14232,7 +14191,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="416" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>237</v>
       </c>
@@ -14261,7 +14220,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="417" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>237</v>
       </c>
@@ -14290,7 +14249,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="418" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>237</v>
       </c>
@@ -14319,7 +14278,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="419" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>237</v>
       </c>
@@ -14348,7 +14307,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="420" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>237</v>
       </c>
@@ -14377,7 +14336,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="421" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>237</v>
       </c>
@@ -14406,7 +14365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="422" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>237</v>
       </c>
@@ -14435,7 +14394,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="423" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>237</v>
       </c>
@@ -14464,7 +14423,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="424" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>237</v>
       </c>
@@ -14493,7 +14452,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="425" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>237</v>
       </c>
@@ -14522,7 +14481,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="426" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>237</v>
       </c>
@@ -14551,7 +14510,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="427" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>237</v>
       </c>
@@ -14580,7 +14539,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="428" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>237</v>
       </c>
@@ -14609,7 +14568,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="429" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>237</v>
       </c>
@@ -14638,7 +14597,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="430" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>237</v>
       </c>
@@ -14667,7 +14626,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="431" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>237</v>
       </c>
@@ -14696,7 +14655,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="432" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>237</v>
       </c>
@@ -14725,7 +14684,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="433" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>237</v>
       </c>
@@ -14754,7 +14713,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="434" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>237</v>
       </c>
@@ -14783,7 +14742,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="435" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>237</v>
       </c>
@@ -14812,7 +14771,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="436" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>237</v>
       </c>
@@ -14841,7 +14800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="437" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>237</v>
       </c>
@@ -14870,7 +14829,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="438" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>237</v>
       </c>
@@ -14899,7 +14858,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="439" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>237</v>
       </c>
@@ -14928,7 +14887,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="440" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>237</v>
       </c>
@@ -14957,7 +14916,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="441" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>237</v>
       </c>
@@ -14986,7 +14945,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="442" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>237</v>
       </c>
@@ -15015,7 +14974,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="443" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>237</v>
       </c>
@@ -15044,7 +15003,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="444" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>237</v>
       </c>
@@ -15073,7 +15032,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="445" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>237</v>
       </c>
@@ -15102,7 +15061,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="446" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>237</v>
       </c>
@@ -15131,7 +15090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="447" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>237</v>
       </c>
@@ -15160,7 +15119,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="448" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>237</v>
       </c>
@@ -15189,7 +15148,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="449" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>237</v>
       </c>
@@ -15218,7 +15177,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="450" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>237</v>
       </c>
@@ -15247,7 +15206,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="451" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>237</v>
       </c>
@@ -15276,7 +15235,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="452" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>237</v>
       </c>
@@ -15305,7 +15264,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="453" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>237</v>
       </c>
@@ -15334,7 +15293,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="454" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>237</v>
       </c>
@@ -15363,7 +15322,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="455" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>237</v>
       </c>
@@ -15392,7 +15351,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="456" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>237</v>
       </c>
@@ -15421,7 +15380,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="457" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>237</v>
       </c>
@@ -15450,7 +15409,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="458" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>237</v>
       </c>
@@ -15479,7 +15438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="459" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>237</v>
       </c>
@@ -15508,7 +15467,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="460" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>237</v>
       </c>
@@ -15537,7 +15496,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="461" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>237</v>
       </c>
@@ -15566,7 +15525,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="462" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>237</v>
       </c>
@@ -15595,7 +15554,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="463" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>237</v>
       </c>
@@ -15624,7 +15583,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="464" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>237</v>
       </c>
@@ -15653,7 +15612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="465" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>237</v>
       </c>
@@ -15682,7 +15641,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="466" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>237</v>
       </c>
@@ -15711,7 +15670,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="467" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>237</v>
       </c>
@@ -15740,7 +15699,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="468" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>237</v>
       </c>
@@ -15769,7 +15728,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="469" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>237</v>
       </c>
@@ -15798,7 +15757,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="470" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>237</v>
       </c>
@@ -15827,7 +15786,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="471" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>237</v>
       </c>
@@ -15856,7 +15815,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="472" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>237</v>
       </c>
@@ -15885,7 +15844,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="473" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>237</v>
       </c>
@@ -15914,7 +15873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="474" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>237</v>
       </c>
@@ -15943,7 +15902,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>237</v>
       </c>
@@ -15972,7 +15931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="476" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>237</v>
       </c>
@@ -16001,7 +15960,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="477" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>237</v>
       </c>
@@ -16030,7 +15989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="478" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>237</v>
       </c>
@@ -16059,7 +16018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="479" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>237</v>
       </c>
@@ -16088,7 +16047,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="480" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>237</v>
       </c>
@@ -16117,7 +16076,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="481" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>237</v>
       </c>
@@ -16145,12 +16104,8 @@
       <c r="I481">
         <v>373</v>
       </c>
-      <c r="J481"/>
-      <c r="K481"/>
-      <c r="L481"/>
-      <c r="M481"/>
-    </row>
-    <row r="482" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="482" spans="1:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>237</v>
       </c>
@@ -16178,18 +16133,26 @@
       <c r="I482">
         <v>93</v>
       </c>
-      <c r="J482"/>
-      <c r="K482"/>
-      <c r="L482"/>
-      <c r="M482"/>
-    </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A483" t="s">
+    </row>
+    <row r="483" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A483" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B483" t="s">
+      <c r="B483" s="1" t="s">
         <v>504</v>
       </c>
+      <c r="C483"/>
+      <c r="D483"/>
+      <c r="E483"/>
+      <c r="F483"/>
+      <c r="G483"/>
+      <c r="H483"/>
+      <c r="I483"/>
+      <c r="J483" s="2"/>
+      <c r="K483" s="2"/>
+      <c r="L483" s="2"/>
+      <c r="M483" s="2"/>
+      <c r="N483"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I482" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -16205,6 +16168,81 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fd5dee7c-ba60-42c5-972c-0266fa4c6388">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="159907c2-825f-4798-be3c-cace777c1bf6" xsi:nil="true"/>
+    <_dlc_DocId xmlns="159907c2-825f-4798-be3c-cace777c1bf6">EXME54VS2YUU-1818840572-15979</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="159907c2-825f-4798-be3c-cace777c1bf6">
+      <Url>https://universityoflatvia387.sharepoint.com/sites/HiQBioDiv/_layouts/15/DocIdRedir.aspx?ID=EXME54VS2YUU-1818840572-15979</Url>
+      <Description>EXME54VS2YUU-1818840572-15979</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100147FB57513909B4BA2EA8B3E2CB0A604" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4d01b0cde4e466c4988ee76d55e29fc9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="159907c2-825f-4798-be3c-cace777c1bf6" xmlns:ns3="fd5dee7c-ba60-42c5-972c-0266fa4c6388" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="555f493e4267aa03dcad174e56e1dacc" ns2:_="" ns3:_="">
     <xsd:import namespace="159907c2-825f-4798-be3c-cace777c1bf6"/>
@@ -16430,82 +16468,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fd5dee7c-ba60-42c5-972c-0266fa4c6388">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="159907c2-825f-4798-be3c-cace777c1bf6" xsi:nil="true"/>
-    <_dlc_DocId xmlns="159907c2-825f-4798-be3c-cace777c1bf6">EXME54VS2YUU-1818840572-15979</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="159907c2-825f-4798-be3c-cace777c1bf6">
-      <Url>https://universityoflatvia387.sharepoint.com/sites/HiQBioDiv/_layouts/15/DocIdRedir.aspx?ID=EXME54VS2YUU-1818840572-15979</Url>
-      <Description>EXME54VS2YUU-1818840572-15979</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44E9BD31-6645-4B98-9051-45A80DD204A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA2A3BDA-8A7D-4EEE-AFCF-72DBE4A88DE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A0CBA5-068E-440E-9C54-AD8F66C32F7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fd5dee7c-ba60-42c5-972c-0266fa4c6388"/>
+    <ds:schemaRef ds:uri="159907c2-825f-4798-be3c-cace777c1bf6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AA545E5-31B2-4840-A2D5-6C612417FD79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16522,31 +16512,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A0CBA5-068E-440E-9C54-AD8F66C32F7A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fd5dee7c-ba60-42c5-972c-0266fa4c6388"/>
-    <ds:schemaRef ds:uri="159907c2-825f-4798-be3c-cace777c1bf6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA2A3BDA-8A7D-4EEE-AFCF-72DBE4A88DE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44E9BD31-6645-4B98-9051-45A80DD204A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/NoverojumuSkaits_wide_NoNo.xlsx
+++ b/NoverojumuSkaits_wide_NoNo.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\taurinu_modeli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33B01B3-B4BC-4BE6-9AA4-2FA7E6EE4F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DC7E14-A0D1-4E8B-A408-224E6AAEF787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="1215" windowWidth="16860" windowHeight="12465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$I$482</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$I$483</definedName>
   </definedNames>
   <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="511">
   <si>
     <t>Group</t>
   </si>
@@ -697,9 +697,6 @@
   </si>
   <si>
     <t>PoroidFungi</t>
-  </si>
-  <si>
-    <t>FLACIT</t>
   </si>
   <si>
     <t>FUSFER</t>
@@ -1647,7 +1644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1657,6 +1654,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1957,7 +1955,7 @@
   <dimension ref="A1:P483"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="8"/>
+    <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1989,19 +1987,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2030,7 +2028,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2059,7 +2057,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="4" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2088,7 +2086,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2117,7 +2115,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2146,7 +2144,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2175,7 +2173,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="8" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2204,7 +2202,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2233,7 +2231,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="10" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2262,7 +2260,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="11" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2291,7 +2289,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="12" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -2320,7 +2318,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2349,7 +2347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2378,7 +2376,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -2407,7 +2405,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="16" spans="1:13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2436,7 +2434,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -2465,7 +2463,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -2494,7 +2492,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2523,7 +2521,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -2552,7 +2550,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -2581,7 +2579,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="22" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2610,7 +2608,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2639,7 +2637,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2668,7 +2666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2697,7 +2695,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="26" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2726,7 +2724,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -2755,7 +2753,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2784,7 +2782,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -2813,7 +2811,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -2842,7 +2840,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -2871,7 +2869,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -2900,7 +2898,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="33" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -2929,7 +2927,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -2958,7 +2956,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="35" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -2987,7 +2985,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="36" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -3016,7 +3014,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="37" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -3045,7 +3043,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -3074,7 +3072,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="39" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -3103,7 +3101,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="40" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -3132,7 +3130,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>24</v>
       </c>
@@ -3161,7 +3159,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="42" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -3190,7 +3188,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="43" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>24</v>
       </c>
@@ -3219,7 +3217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>24</v>
       </c>
@@ -3248,7 +3246,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -3277,7 +3275,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -3306,7 +3304,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -3335,7 +3333,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -3364,7 +3362,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -3393,7 +3391,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -3422,7 +3420,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -3451,7 +3449,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -3480,7 +3478,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -3509,7 +3507,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="54" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>24</v>
       </c>
@@ -3538,7 +3536,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>24</v>
       </c>
@@ -3567,7 +3565,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>24</v>
       </c>
@@ -3596,7 +3594,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -3625,7 +3623,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>24</v>
       </c>
@@ -3654,7 +3652,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>24</v>
       </c>
@@ -3683,7 +3681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>24</v>
       </c>
@@ -3712,7 +3710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>24</v>
       </c>
@@ -3741,7 +3739,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -3770,7 +3768,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="63" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -3799,7 +3797,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>24</v>
       </c>
@@ -3828,7 +3826,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>24</v>
       </c>
@@ -3857,7 +3855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -3886,7 +3884,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="67" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -3915,7 +3913,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="68" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -3944,7 +3942,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -3973,7 +3971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>78</v>
       </c>
@@ -4002,7 +4000,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="71" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -4031,7 +4029,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>78</v>
       </c>
@@ -4060,7 +4058,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="73" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -4089,7 +4087,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -4118,7 +4116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -4147,7 +4145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -4176,7 +4174,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="77" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -4205,7 +4203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -4234,7 +4232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -4263,7 +4261,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -4292,7 +4290,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="81" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>78</v>
       </c>
@@ -4321,7 +4319,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="82" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>78</v>
       </c>
@@ -4350,7 +4348,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>78</v>
       </c>
@@ -4379,7 +4377,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>78</v>
       </c>
@@ -4408,7 +4406,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="85" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>78</v>
       </c>
@@ -4437,7 +4435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -4466,7 +4464,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -4495,7 +4493,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -4524,7 +4522,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="89" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -4553,7 +4551,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -4582,7 +4580,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="91" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>97</v>
       </c>
@@ -4611,7 +4609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>97</v>
       </c>
@@ -4640,7 +4638,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="93" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -4669,7 +4667,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="94" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -4698,7 +4696,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="95" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -4727,7 +4725,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="96" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -4756,7 +4754,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -4785,7 +4783,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -4814,7 +4812,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="99" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>97</v>
       </c>
@@ -4843,7 +4841,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="100" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>97</v>
       </c>
@@ -4872,7 +4870,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="101" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>97</v>
       </c>
@@ -4901,7 +4899,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="102" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -4930,7 +4928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>97</v>
       </c>
@@ -4959,7 +4957,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>97</v>
       </c>
@@ -4988,7 +4986,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>97</v>
       </c>
@@ -5017,7 +5015,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="106" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>97</v>
       </c>
@@ -5046,7 +5044,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>97</v>
       </c>
@@ -5075,7 +5073,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>97</v>
       </c>
@@ -5104,7 +5102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>97</v>
       </c>
@@ -5133,7 +5131,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>97</v>
       </c>
@@ -5162,7 +5160,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>97</v>
       </c>
@@ -5191,7 +5189,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="112" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>97</v>
       </c>
@@ -5220,7 +5218,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -5249,7 +5247,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>97</v>
       </c>
@@ -5278,7 +5276,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="115" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>97</v>
       </c>
@@ -5307,7 +5305,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="116" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>97</v>
       </c>
@@ -5336,7 +5334,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>97</v>
       </c>
@@ -5365,7 +5363,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="118" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>97</v>
       </c>
@@ -5394,7 +5392,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="119" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>97</v>
       </c>
@@ -5423,7 +5421,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>97</v>
       </c>
@@ -5452,7 +5450,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="121" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>97</v>
       </c>
@@ -5481,7 +5479,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>97</v>
       </c>
@@ -5510,7 +5508,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>97</v>
       </c>
@@ -5539,7 +5537,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="124" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>97</v>
       </c>
@@ -5568,7 +5566,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>97</v>
       </c>
@@ -5597,7 +5595,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>97</v>
       </c>
@@ -5626,7 +5624,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="127" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>97</v>
       </c>
@@ -5655,7 +5653,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="128" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>140</v>
       </c>
@@ -5684,7 +5682,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="129" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>140</v>
       </c>
@@ -5713,7 +5711,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="130" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>140</v>
       </c>
@@ -5742,7 +5740,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>140</v>
       </c>
@@ -5771,7 +5769,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="132" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>140</v>
       </c>
@@ -5800,7 +5798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="133" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -5829,7 +5827,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>147</v>
       </c>
@@ -5858,7 +5856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>147</v>
       </c>
@@ -5887,7 +5885,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>147</v>
       </c>
@@ -5916,7 +5914,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="137" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>147</v>
       </c>
@@ -5945,7 +5943,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="138" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>147</v>
       </c>
@@ -5974,7 +5972,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="139" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>147</v>
       </c>
@@ -6003,7 +6001,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="140" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>147</v>
       </c>
@@ -6032,7 +6030,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="141" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>147</v>
       </c>
@@ -6061,7 +6059,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="142" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>147</v>
       </c>
@@ -6090,7 +6088,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="143" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>147</v>
       </c>
@@ -6119,7 +6117,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="144" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>147</v>
       </c>
@@ -6148,7 +6146,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="145" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -6177,7 +6175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="146" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>147</v>
       </c>
@@ -6206,7 +6204,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="147" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>147</v>
       </c>
@@ -6235,7 +6233,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="148" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>147</v>
       </c>
@@ -6264,7 +6262,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="149" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>147</v>
       </c>
@@ -6293,7 +6291,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>147</v>
       </c>
@@ -6322,7 +6320,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="151" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>147</v>
       </c>
@@ -6351,7 +6349,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>166</v>
       </c>
@@ -6380,7 +6378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>166</v>
       </c>
@@ -6409,7 +6407,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="154" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>166</v>
       </c>
@@ -6438,7 +6436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>166</v>
       </c>
@@ -6467,7 +6465,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>166</v>
       </c>
@@ -6496,7 +6494,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>166</v>
       </c>
@@ -6525,7 +6523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>166</v>
       </c>
@@ -6554,7 +6552,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="159" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -6583,7 +6581,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="160" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>166</v>
       </c>
@@ -6612,7 +6610,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="161" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>166</v>
       </c>
@@ -6641,7 +6639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="162" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -6670,7 +6668,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="163" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>166</v>
       </c>
@@ -6699,7 +6697,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="164" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>179</v>
       </c>
@@ -6728,7 +6726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>179</v>
       </c>
@@ -6757,7 +6755,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="166" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>179</v>
       </c>
@@ -6786,7 +6784,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="167" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>179</v>
       </c>
@@ -6815,7 +6813,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="168" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>184</v>
       </c>
@@ -6844,7 +6842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="169" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>184</v>
       </c>
@@ -6873,7 +6871,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="170" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>184</v>
       </c>
@@ -6902,7 +6900,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="171" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>184</v>
       </c>
@@ -6931,7 +6929,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="172" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>184</v>
       </c>
@@ -6960,7 +6958,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>184</v>
       </c>
@@ -6989,7 +6987,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>184</v>
       </c>
@@ -7018,7 +7016,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="175" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>184</v>
       </c>
@@ -7047,7 +7045,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>184</v>
       </c>
@@ -7076,7 +7074,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="177" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>184</v>
       </c>
@@ -7112,22 +7110,22 @@
       <c r="B178" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C178" s="1">
+      <c r="C178" s="8">
         <v>415</v>
       </c>
-      <c r="D178" s="1">
+      <c r="D178" s="8">
         <v>415</v>
       </c>
-      <c r="E178" s="1">
+      <c r="E178" s="8">
         <v>415</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="8">
         <v>415</v>
       </c>
-      <c r="G178" s="1">
+      <c r="G178" s="8">
         <v>415</v>
       </c>
-      <c r="H178" s="1">
+      <c r="H178" s="8">
         <v>405</v>
       </c>
       <c r="I178" s="1">
@@ -7326,31 +7324,31 @@
       <c r="B184" t="s">
         <v>202</v>
       </c>
-      <c r="C184">
+      <c r="C184" s="8">
         <v>58</v>
       </c>
-      <c r="D184">
+      <c r="D184" s="8">
         <v>58</v>
       </c>
-      <c r="E184">
+      <c r="E184" s="8">
         <v>58</v>
       </c>
-      <c r="F184">
+      <c r="F184" s="8">
         <v>58</v>
       </c>
-      <c r="G184">
+      <c r="G184" s="8">
         <v>58</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="8">
         <v>56</v>
       </c>
       <c r="I184">
         <v>46</v>
       </c>
-      <c r="J184" s="2"/>
-      <c r="K184" s="2"/>
-      <c r="L184" s="2"/>
-      <c r="M184" s="2"/>
+      <c r="J184" s="9"/>
+      <c r="K184" s="9"/>
+      <c r="L184" s="9"/>
+      <c r="M184" s="9"/>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
@@ -7359,37 +7357,37 @@
       <c r="B185" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C185" s="1">
+      <c r="C185" s="8">
         <v>234</v>
       </c>
-      <c r="D185" s="1">
+      <c r="D185" s="8">
         <v>234</v>
       </c>
-      <c r="E185" s="1">
+      <c r="E185" s="8">
         <v>232</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="8">
         <v>232</v>
       </c>
-      <c r="G185" s="1">
+      <c r="G185" s="8">
         <v>232</v>
       </c>
-      <c r="H185" s="1">
+      <c r="H185" s="8">
         <v>210</v>
       </c>
       <c r="I185" s="1">
         <v>172</v>
       </c>
-      <c r="J185" s="2">
+      <c r="J185" s="9">
         <v>0</v>
       </c>
-      <c r="K185" s="2">
+      <c r="K185" s="9">
         <v>0</v>
       </c>
-      <c r="L185" s="2">
+      <c r="L185" s="9">
         <v>1</v>
       </c>
-      <c r="M185" s="2">
+      <c r="M185" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7400,45 +7398,45 @@
       <c r="B186" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C186" s="1">
+      <c r="C186" s="8">
         <v>331</v>
       </c>
-      <c r="D186" s="1">
+      <c r="D186" s="8">
         <v>331</v>
       </c>
-      <c r="E186" s="1">
+      <c r="E186" s="8">
         <v>331</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="8">
         <v>331</v>
       </c>
-      <c r="G186" s="1">
+      <c r="G186" s="8">
         <v>331</v>
       </c>
-      <c r="H186" s="1">
+      <c r="H186" s="8">
         <v>325</v>
       </c>
       <c r="I186" s="1">
         <v>293</v>
       </c>
-      <c r="J186" s="2">
+      <c r="J186" s="9">
         <v>0</v>
       </c>
-      <c r="K186" s="2">
+      <c r="K186" s="9">
         <v>0</v>
       </c>
-      <c r="L186" s="2">
+      <c r="L186" s="9">
         <v>1</v>
       </c>
-      <c r="M186" s="2">
+      <c r="M186" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A187" s="8" t="s">
+      <c r="A187" t="s">
         <v>195</v>
       </c>
-      <c r="B187" s="8" t="s">
+      <c r="B187" t="s">
         <v>205</v>
       </c>
       <c r="C187" s="8">
@@ -7459,19 +7457,19 @@
       <c r="H187" s="8">
         <v>41</v>
       </c>
-      <c r="I187" s="8">
+      <c r="I187">
         <v>29</v>
       </c>
-      <c r="J187" s="2">
+      <c r="J187" s="9">
         <v>1</v>
       </c>
-      <c r="K187" s="2">
+      <c r="K187" s="9">
         <v>0</v>
       </c>
-      <c r="L187" s="3">
+      <c r="L187" s="9">
         <v>1</v>
       </c>
-      <c r="M187" s="2">
+      <c r="M187" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7482,37 +7480,37 @@
       <c r="B188" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C188" s="1">
+      <c r="C188" s="8">
         <v>88</v>
       </c>
-      <c r="D188" s="1">
+      <c r="D188" s="8">
         <v>88</v>
       </c>
-      <c r="E188" s="1">
+      <c r="E188" s="8">
         <v>88</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="8">
         <v>88</v>
       </c>
-      <c r="G188" s="1">
+      <c r="G188" s="8">
         <v>88</v>
       </c>
-      <c r="H188" s="1">
+      <c r="H188" s="8">
         <v>74</v>
       </c>
       <c r="I188" s="1">
         <v>60</v>
       </c>
-      <c r="J188" s="2">
+      <c r="J188" s="9">
         <v>0</v>
       </c>
-      <c r="K188" s="2">
+      <c r="K188" s="9">
         <v>0</v>
       </c>
-      <c r="L188" s="2">
+      <c r="L188" s="9">
         <v>1</v>
       </c>
-      <c r="M188" s="2">
+      <c r="M188" s="9">
         <v>1</v>
       </c>
     </row>
@@ -7523,31 +7521,31 @@
       <c r="B189" t="s">
         <v>207</v>
       </c>
-      <c r="C189">
+      <c r="C189" s="8">
         <v>252</v>
       </c>
-      <c r="D189">
+      <c r="D189" s="8">
         <v>252</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="8">
         <v>252</v>
       </c>
-      <c r="F189">
+      <c r="F189" s="8">
         <v>252</v>
       </c>
-      <c r="G189">
+      <c r="G189" s="8">
         <v>252</v>
       </c>
-      <c r="H189">
+      <c r="H189" s="8">
         <v>220</v>
       </c>
       <c r="I189">
         <v>164</v>
       </c>
-      <c r="J189" s="2"/>
-      <c r="K189" s="2"/>
-      <c r="L189" s="2"/>
-      <c r="M189" s="2"/>
+      <c r="J189" s="9"/>
+      <c r="K189" s="9"/>
+      <c r="L189" s="9"/>
+      <c r="M189" s="9"/>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
@@ -7556,31 +7554,31 @@
       <c r="B190" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C190">
-        <v>667</v>
-      </c>
-      <c r="D190">
-        <v>667</v>
-      </c>
-      <c r="E190">
-        <v>667</v>
-      </c>
-      <c r="F190">
-        <v>667</v>
-      </c>
-      <c r="G190">
-        <v>0</v>
-      </c>
-      <c r="H190">
-        <v>0</v>
+      <c r="C190" s="8">
+        <v>104</v>
+      </c>
+      <c r="D190" s="8">
+        <v>104</v>
+      </c>
+      <c r="E190" s="8">
+        <v>104</v>
+      </c>
+      <c r="F190" s="8">
+        <v>104</v>
+      </c>
+      <c r="G190" s="8">
+        <v>104</v>
+      </c>
+      <c r="H190" s="8">
+        <v>95</v>
       </c>
       <c r="I190">
-        <v>0</v>
-      </c>
-      <c r="J190" s="2"/>
-      <c r="K190" s="2"/>
-      <c r="L190" s="2"/>
-      <c r="M190" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="J190" s="9"/>
+      <c r="K190" s="9"/>
+      <c r="L190" s="9"/>
+      <c r="M190" s="9"/>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
@@ -7589,34 +7587,34 @@
       <c r="B191" t="s">
         <v>209</v>
       </c>
-      <c r="C191">
+      <c r="C191" s="8">
         <v>277</v>
       </c>
-      <c r="D191">
+      <c r="D191" s="8">
         <v>277</v>
       </c>
-      <c r="E191">
+      <c r="E191" s="8">
         <v>277</v>
       </c>
-      <c r="F191">
+      <c r="F191" s="8">
         <v>277</v>
       </c>
-      <c r="G191">
+      <c r="G191" s="8">
         <v>277</v>
       </c>
-      <c r="H191">
+      <c r="H191" s="8">
         <v>246</v>
       </c>
       <c r="I191">
         <v>177</v>
       </c>
-      <c r="J191" s="2"/>
-      <c r="K191" s="2"/>
-      <c r="L191" s="2"/>
-      <c r="M191" s="2"/>
+      <c r="J191" s="9"/>
+      <c r="K191" s="9"/>
+      <c r="L191" s="9"/>
+      <c r="M191" s="9"/>
       <c r="O191" s="5"/>
-      <c r="P191" s="8" t="s">
-        <v>509</v>
+      <c r="P191" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.25">
@@ -7626,34 +7624,34 @@
       <c r="B192" t="s">
         <v>210</v>
       </c>
-      <c r="C192">
+      <c r="C192" s="8">
         <v>279</v>
       </c>
-      <c r="D192">
+      <c r="D192" s="8">
         <v>279</v>
       </c>
-      <c r="E192">
+      <c r="E192" s="8">
         <v>279</v>
       </c>
-      <c r="F192">
+      <c r="F192" s="8">
         <v>279</v>
       </c>
-      <c r="G192">
+      <c r="G192" s="8">
         <v>279</v>
       </c>
-      <c r="H192">
+      <c r="H192" s="8">
         <v>273</v>
       </c>
       <c r="I192">
         <v>237</v>
       </c>
-      <c r="J192" s="2"/>
-      <c r="K192" s="2"/>
-      <c r="L192" s="2"/>
-      <c r="M192" s="2"/>
+      <c r="J192" s="9"/>
+      <c r="K192" s="9"/>
+      <c r="L192" s="9"/>
+      <c r="M192" s="9"/>
       <c r="O192" s="4"/>
-      <c r="P192" s="8" t="s">
-        <v>510</v>
+      <c r="P192" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.25">
@@ -7663,42 +7661,42 @@
       <c r="B193" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C193" s="1">
+      <c r="C193" s="8">
         <v>587</v>
       </c>
-      <c r="D193" s="1">
+      <c r="D193" s="8">
         <v>587</v>
       </c>
-      <c r="E193" s="1">
+      <c r="E193" s="8">
         <v>587</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="8">
         <v>587</v>
       </c>
-      <c r="G193" s="1">
+      <c r="G193" s="8">
         <v>587</v>
       </c>
-      <c r="H193" s="1">
+      <c r="H193" s="8">
         <v>539</v>
       </c>
       <c r="I193" s="1">
         <v>419</v>
       </c>
-      <c r="J193" s="2">
+      <c r="J193" s="9">
         <v>0</v>
       </c>
-      <c r="K193" s="2">
+      <c r="K193" s="9">
         <v>0</v>
       </c>
-      <c r="L193" s="2">
+      <c r="L193" s="9">
         <v>1</v>
       </c>
-      <c r="M193" s="2">
+      <c r="M193" s="9">
         <v>1</v>
       </c>
       <c r="O193" s="6"/>
-      <c r="P193" s="8" t="s">
-        <v>511</v>
+      <c r="P193" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.25">
@@ -7708,37 +7706,37 @@
       <c r="B194" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C194" s="1">
+      <c r="C194" s="8">
         <v>796</v>
       </c>
-      <c r="D194" s="1">
+      <c r="D194" s="8">
         <v>796</v>
       </c>
-      <c r="E194" s="1">
+      <c r="E194" s="8">
         <v>796</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="8">
         <v>796</v>
       </c>
-      <c r="G194" s="1">
+      <c r="G194" s="8">
         <v>796</v>
       </c>
-      <c r="H194" s="1">
+      <c r="H194" s="8">
         <v>734</v>
       </c>
       <c r="I194" s="1">
         <v>604</v>
       </c>
-      <c r="J194" s="2">
+      <c r="J194" s="9">
         <v>0</v>
       </c>
-      <c r="K194" s="2">
+      <c r="K194" s="9">
         <v>0</v>
       </c>
-      <c r="L194" s="2">
+      <c r="L194" s="9">
         <v>1</v>
       </c>
-      <c r="M194" s="2">
+      <c r="M194" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7749,31 +7747,31 @@
       <c r="B195" t="s">
         <v>213</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="8">
         <v>167</v>
       </c>
-      <c r="D195">
+      <c r="D195" s="8">
         <v>167</v>
       </c>
-      <c r="E195">
+      <c r="E195" s="8">
         <v>167</v>
       </c>
-      <c r="F195">
+      <c r="F195" s="8">
         <v>167</v>
       </c>
-      <c r="G195">
+      <c r="G195" s="8">
         <v>167</v>
       </c>
-      <c r="H195">
+      <c r="H195" s="8">
         <v>151</v>
       </c>
       <c r="I195">
         <v>133</v>
       </c>
-      <c r="J195" s="2"/>
-      <c r="K195" s="2"/>
-      <c r="L195" s="2"/>
-      <c r="M195" s="2"/>
+      <c r="J195" s="9"/>
+      <c r="K195" s="9"/>
+      <c r="L195" s="9"/>
+      <c r="M195" s="9"/>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
@@ -7782,37 +7780,37 @@
       <c r="B196" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C196" s="1">
+      <c r="C196" s="8">
         <v>977</v>
       </c>
-      <c r="D196" s="1">
+      <c r="D196" s="8">
         <v>977</v>
       </c>
-      <c r="E196" s="1">
+      <c r="E196" s="8">
         <v>977</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="8">
         <v>977</v>
       </c>
-      <c r="G196" s="1">
+      <c r="G196" s="8">
         <v>977</v>
       </c>
-      <c r="H196" s="1">
+      <c r="H196" s="8">
         <v>916</v>
       </c>
       <c r="I196" s="1">
         <v>743</v>
       </c>
-      <c r="J196" s="2">
+      <c r="J196" s="9">
         <v>0</v>
       </c>
-      <c r="K196" s="2">
+      <c r="K196" s="9">
         <v>0</v>
       </c>
-      <c r="L196" s="2">
+      <c r="L196" s="9">
         <v>1</v>
       </c>
-      <c r="M196" s="2">
+      <c r="M196" s="9">
         <v>1</v>
       </c>
     </row>
@@ -7823,37 +7821,37 @@
       <c r="B197" t="s">
         <v>215</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="8">
         <v>492</v>
       </c>
-      <c r="D197">
+      <c r="D197" s="8">
         <v>492</v>
       </c>
-      <c r="E197">
+      <c r="E197" s="8">
         <v>490</v>
       </c>
-      <c r="F197">
+      <c r="F197" s="8">
         <v>490</v>
       </c>
-      <c r="G197">
+      <c r="G197" s="8">
         <v>490</v>
       </c>
-      <c r="H197">
+      <c r="H197" s="8">
         <v>454</v>
       </c>
       <c r="I197">
         <v>405</v>
       </c>
-      <c r="J197" s="2">
+      <c r="J197" s="9">
         <v>0</v>
       </c>
-      <c r="K197" s="2">
+      <c r="K197" s="9">
         <v>0</v>
       </c>
-      <c r="L197" s="2">
+      <c r="L197" s="9">
         <v>1</v>
       </c>
-      <c r="M197" s="2">
+      <c r="M197" s="9">
         <v>1</v>
       </c>
     </row>
@@ -7864,31 +7862,31 @@
       <c r="B198" t="s">
         <v>216</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="8">
         <v>191</v>
       </c>
-      <c r="D198">
+      <c r="D198" s="8">
         <v>191</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="8">
         <v>191</v>
       </c>
-      <c r="F198">
+      <c r="F198" s="8">
         <v>191</v>
       </c>
-      <c r="G198">
+      <c r="G198" s="8">
         <v>191</v>
       </c>
-      <c r="H198">
+      <c r="H198" s="8">
         <v>168</v>
       </c>
       <c r="I198">
         <v>117</v>
       </c>
-      <c r="J198" s="2"/>
-      <c r="K198" s="2"/>
-      <c r="L198" s="2"/>
-      <c r="M198" s="2"/>
+      <c r="J198" s="9"/>
+      <c r="K198" s="9"/>
+      <c r="L198" s="9"/>
+      <c r="M198" s="9"/>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
@@ -7897,31 +7895,31 @@
       <c r="B199" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="8">
         <v>842</v>
       </c>
-      <c r="D199">
+      <c r="D199" s="8">
         <v>842</v>
       </c>
-      <c r="E199">
+      <c r="E199" s="8">
         <v>842</v>
       </c>
-      <c r="F199">
+      <c r="F199" s="8">
         <v>842</v>
       </c>
-      <c r="G199">
+      <c r="G199" s="8">
         <v>842</v>
       </c>
-      <c r="H199">
+      <c r="H199" s="8">
         <v>765</v>
       </c>
       <c r="I199">
         <v>575</v>
       </c>
-      <c r="J199" s="2"/>
-      <c r="K199" s="2"/>
-      <c r="L199" s="2"/>
-      <c r="M199" s="2"/>
+      <c r="J199" s="9"/>
+      <c r="K199" s="9"/>
+      <c r="L199" s="9"/>
+      <c r="M199" s="9"/>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
@@ -7930,67 +7928,71 @@
       <c r="B200" t="s">
         <v>218</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="8">
         <v>66</v>
       </c>
-      <c r="D200">
+      <c r="D200" s="8">
         <v>66</v>
       </c>
-      <c r="E200">
+      <c r="E200" s="8">
         <v>66</v>
       </c>
-      <c r="F200">
+      <c r="F200" s="8">
         <v>66</v>
       </c>
-      <c r="G200">
+      <c r="G200" s="8">
         <v>66</v>
       </c>
-      <c r="H200">
+      <c r="H200" s="8">
         <v>62</v>
       </c>
       <c r="I200">
         <v>52</v>
       </c>
-      <c r="J200" s="2"/>
-      <c r="K200" s="2"/>
-      <c r="L200" s="2"/>
-      <c r="M200" s="2"/>
-    </row>
-    <row r="201" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>219</v>
-      </c>
-      <c r="B201" t="s">
-        <v>220</v>
-      </c>
-      <c r="C201">
-        <v>131</v>
-      </c>
-      <c r="D201">
-        <v>131</v>
-      </c>
-      <c r="E201">
-        <v>131</v>
-      </c>
-      <c r="F201">
-        <v>131</v>
-      </c>
-      <c r="G201">
-        <v>131</v>
-      </c>
-      <c r="H201">
-        <v>128</v>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
+      <c r="L200" s="9"/>
+      <c r="M200" s="9"/>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C201" s="8">
+        <v>41</v>
+      </c>
+      <c r="D201" s="8">
+        <v>41</v>
+      </c>
+      <c r="E201" s="8">
+        <v>41</v>
+      </c>
+      <c r="F201" s="8">
+        <v>41</v>
+      </c>
+      <c r="G201" s="8">
+        <v>41</v>
+      </c>
+      <c r="H201" s="8">
+        <v>33</v>
       </c>
       <c r="I201">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="202" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="J201" s="2"/>
+      <c r="K201" s="2"/>
+      <c r="L201" s="2"/>
+      <c r="M201" s="2"/>
+    </row>
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>219</v>
       </c>
       <c r="B202" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C202">
         <v>55</v>
@@ -8014,12 +8016,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="203" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>219</v>
       </c>
       <c r="B203" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C203">
         <v>72</v>
@@ -8043,12 +8045,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="204" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>219</v>
       </c>
       <c r="B204" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C204">
         <v>106</v>
@@ -8072,12 +8074,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="205" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>219</v>
       </c>
       <c r="B205" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C205">
         <v>175</v>
@@ -8101,12 +8103,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="206" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>219</v>
       </c>
       <c r="B206" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C206">
         <v>60</v>
@@ -8130,12 +8132,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="207" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>219</v>
       </c>
       <c r="B207" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C207">
         <v>104</v>
@@ -8159,12 +8161,12 @@
         <v>94</v>
       </c>
     </row>
-    <row r="208" spans="1:16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>219</v>
       </c>
       <c r="B208" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C208">
         <v>192</v>
@@ -8188,12 +8190,12 @@
         <v>184</v>
       </c>
     </row>
-    <row r="209" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>219</v>
       </c>
       <c r="B209" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C209">
         <v>221</v>
@@ -8217,12 +8219,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="210" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>219</v>
       </c>
       <c r="B210" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C210">
         <v>82</v>
@@ -8246,12 +8248,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="211" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>229</v>
+      </c>
+      <c r="B211" t="s">
         <v>230</v>
-      </c>
-      <c r="B211" t="s">
-        <v>231</v>
       </c>
       <c r="C211">
         <v>698</v>
@@ -8275,12 +8277,12 @@
         <v>414</v>
       </c>
     </row>
-    <row r="212" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B212" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C212">
         <v>48</v>
@@ -8304,12 +8306,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B213" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C213">
         <v>627</v>
@@ -8333,12 +8335,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="214" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B214" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C214">
         <v>1162</v>
@@ -8362,12 +8364,12 @@
         <v>759</v>
       </c>
     </row>
-    <row r="215" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B215" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C215">
         <v>326</v>
@@ -8391,12 +8393,12 @@
         <v>266</v>
       </c>
     </row>
-    <row r="216" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B216" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C216">
         <v>796</v>
@@ -8420,12 +8422,12 @@
         <v>499</v>
       </c>
     </row>
-    <row r="217" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>236</v>
+      </c>
+      <c r="B217" t="s">
         <v>237</v>
-      </c>
-      <c r="B217" t="s">
-        <v>238</v>
       </c>
       <c r="C217">
         <v>102</v>
@@ -8449,12 +8451,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="218" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B218" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C218">
         <v>13</v>
@@ -8478,12 +8480,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B219" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C219">
         <v>2832</v>
@@ -8507,12 +8509,12 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="220" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B220" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C220">
         <v>652</v>
@@ -8536,12 +8538,12 @@
         <v>421</v>
       </c>
     </row>
-    <row r="221" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B221" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C221">
         <v>116</v>
@@ -8565,12 +8567,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="222" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B222" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C222">
         <v>408</v>
@@ -8594,12 +8596,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="223" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B223" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C223">
         <v>81</v>
@@ -8623,12 +8625,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B224" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C224">
         <v>113</v>
@@ -8652,12 +8654,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="225" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B225" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C225">
         <v>96</v>
@@ -8681,12 +8683,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B226" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C226">
         <v>24</v>
@@ -8710,12 +8712,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B227" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C227">
         <v>80</v>
@@ -8739,12 +8741,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="228" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B228" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C228">
         <v>446</v>
@@ -8768,12 +8770,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="229" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B229" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C229">
         <v>105</v>
@@ -8797,12 +8799,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="230" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B230" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C230">
         <v>86</v>
@@ -8826,12 +8828,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="231" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B231" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C231">
         <v>19</v>
@@ -8855,12 +8857,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B232" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C232">
         <v>101</v>
@@ -8884,12 +8886,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="233" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B233" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C233">
         <v>57</v>
@@ -8913,12 +8915,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="234" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B234" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C234">
         <v>68</v>
@@ -8942,12 +8944,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B235" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C235">
         <v>2750</v>
@@ -8971,12 +8973,12 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="236" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B236" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C236">
         <v>82</v>
@@ -9000,12 +9002,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="237" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C237">
         <v>66</v>
@@ -9029,12 +9031,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="238" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C238">
         <v>89</v>
@@ -9058,12 +9060,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B239" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C239">
         <v>83</v>
@@ -9087,12 +9089,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="240" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B240" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C240">
         <v>31</v>
@@ -9116,12 +9118,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="241" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B241" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C241">
         <v>27</v>
@@ -9145,12 +9147,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B242" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C242">
         <v>474</v>
@@ -9174,12 +9176,12 @@
         <v>382</v>
       </c>
     </row>
-    <row r="243" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B243" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C243">
         <v>24</v>
@@ -9203,12 +9205,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="244" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B244" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C244">
         <v>69</v>
@@ -9232,12 +9234,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="245" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B245" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C245">
         <v>62</v>
@@ -9261,12 +9263,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B246" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C246">
         <v>19</v>
@@ -9290,12 +9292,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B247" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C247">
         <v>138</v>
@@ -9319,12 +9321,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="248" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B248" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C248">
         <v>82</v>
@@ -9348,12 +9350,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="249" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B249" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C249">
         <v>56</v>
@@ -9377,12 +9379,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="250" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B250" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C250">
         <v>33</v>
@@ -9406,12 +9408,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="251" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B251" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C251">
         <v>27</v>
@@ -9435,12 +9437,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="252" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B252" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C252">
         <v>6793</v>
@@ -9464,12 +9466,12 @@
         <v>4038</v>
       </c>
     </row>
-    <row r="253" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B253" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C253">
         <v>42</v>
@@ -9493,12 +9495,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B254" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C254">
         <v>216</v>
@@ -9522,12 +9524,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="255" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B255" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C255">
         <v>347</v>
@@ -9551,12 +9553,12 @@
         <v>298</v>
       </c>
     </row>
-    <row r="256" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B256" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C256">
         <v>285</v>
@@ -9580,12 +9582,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="257" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B257" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C257">
         <v>3510</v>
@@ -9609,12 +9611,12 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="258" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B258" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C258">
         <v>122</v>
@@ -9638,12 +9640,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="259" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B259" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C259">
         <v>267</v>
@@ -9667,12 +9669,12 @@
         <v>208</v>
       </c>
     </row>
-    <row r="260" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B260" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C260">
         <v>165</v>
@@ -9696,12 +9698,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="261" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B261" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C261">
         <v>6</v>
@@ -9725,12 +9727,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B262" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C262">
         <v>171</v>
@@ -9754,12 +9756,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="263" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B263" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C263">
         <v>77</v>
@@ -9783,12 +9785,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B264" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C264">
         <v>94</v>
@@ -9812,12 +9814,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="265" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B265" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C265">
         <v>569</v>
@@ -9841,12 +9843,12 @@
         <v>432</v>
       </c>
     </row>
-    <row r="266" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B266" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C266">
         <v>25</v>
@@ -9870,12 +9872,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B267" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C267">
         <v>273</v>
@@ -9899,12 +9901,12 @@
         <v>147</v>
       </c>
     </row>
-    <row r="268" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B268" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C268">
         <v>74</v>
@@ -9928,12 +9930,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="269" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B269" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C269">
         <v>390</v>
@@ -9957,12 +9959,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="270" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B270" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C270">
         <v>315</v>
@@ -9986,12 +9988,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="271" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B271" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C271">
         <v>83</v>
@@ -10015,12 +10017,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="272" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B272" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C272">
         <v>318</v>
@@ -10044,12 +10046,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="273" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B273" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C273">
         <v>935</v>
@@ -10073,12 +10075,12 @@
         <v>635</v>
       </c>
     </row>
-    <row r="274" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B274" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C274">
         <v>35</v>
@@ -10102,12 +10104,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="275" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B275" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C275">
         <v>3631</v>
@@ -10131,12 +10133,12 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="276" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B276" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C276">
         <v>57</v>
@@ -10160,12 +10162,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="277" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B277" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C277">
         <v>47</v>
@@ -10189,12 +10191,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B278" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C278">
         <v>36</v>
@@ -10218,12 +10220,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B279" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C279">
         <v>390</v>
@@ -10247,12 +10249,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="280" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B280" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C280">
         <v>1371</v>
@@ -10276,12 +10278,12 @@
         <v>950</v>
       </c>
     </row>
-    <row r="281" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B281" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C281">
         <v>32</v>
@@ -10305,12 +10307,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="282" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B282" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C282">
         <v>24</v>
@@ -10334,12 +10336,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B283" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C283">
         <v>365</v>
@@ -10363,12 +10365,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="284" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B284" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C284">
         <v>44</v>
@@ -10392,12 +10394,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="285" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B285" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C285">
         <v>1995</v>
@@ -10421,12 +10423,12 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="286" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B286" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C286">
         <v>141</v>
@@ -10450,12 +10452,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="287" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B287" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C287">
         <v>295</v>
@@ -10479,12 +10481,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="288" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B288" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C288">
         <v>452</v>
@@ -10508,12 +10510,12 @@
         <v>316</v>
       </c>
     </row>
-    <row r="289" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B289" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C289">
         <v>152</v>
@@ -10537,12 +10539,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="290" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B290" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C290">
         <v>224</v>
@@ -10566,12 +10568,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="291" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B291" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C291">
         <v>476</v>
@@ -10595,12 +10597,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="292" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B292" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C292">
         <v>37</v>
@@ -10624,12 +10626,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="293" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B293" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C293">
         <v>857</v>
@@ -10653,12 +10655,12 @@
         <v>584</v>
       </c>
     </row>
-    <row r="294" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B294" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C294">
         <v>1294</v>
@@ -10682,12 +10684,12 @@
         <v>941</v>
       </c>
     </row>
-    <row r="295" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B295" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C295">
         <v>166</v>
@@ -10711,12 +10713,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="296" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B296" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C296">
         <v>121</v>
@@ -10740,12 +10742,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="297" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B297" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C297">
         <v>190</v>
@@ -10769,12 +10771,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="298" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B298" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C298">
         <v>301</v>
@@ -10798,12 +10800,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="299" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B299" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -10827,12 +10829,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B300" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C300">
         <v>9</v>
@@ -10856,12 +10858,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B301" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C301">
         <v>22</v>
@@ -10885,12 +10887,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="302" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B302" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C302">
         <v>187</v>
@@ -10914,12 +10916,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="303" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B303" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C303">
         <v>188</v>
@@ -10943,12 +10945,12 @@
         <v>173</v>
       </c>
     </row>
-    <row r="304" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B304" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C304">
         <v>29</v>
@@ -10972,12 +10974,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="305" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B305" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C305">
         <v>28</v>
@@ -11001,12 +11003,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="306" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B306" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C306">
         <v>1653</v>
@@ -11030,12 +11032,12 @@
         <v>860</v>
       </c>
     </row>
-    <row r="307" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B307" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C307">
         <v>563</v>
@@ -11059,12 +11061,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="308" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B308" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C308">
         <v>674</v>
@@ -11088,12 +11090,12 @@
         <v>398</v>
       </c>
     </row>
-    <row r="309" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B309" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C309">
         <v>32</v>
@@ -11117,12 +11119,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B310" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C310">
         <v>58</v>
@@ -11146,12 +11148,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="311" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B311" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C311">
         <v>507</v>
@@ -11175,12 +11177,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="312" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B312" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C312">
         <v>1165</v>
@@ -11204,12 +11206,12 @@
         <v>376</v>
       </c>
     </row>
-    <row r="313" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B313" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C313">
         <v>54</v>
@@ -11233,12 +11235,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="314" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B314" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C314">
         <v>1475</v>
@@ -11262,12 +11264,12 @@
         <v>944</v>
       </c>
     </row>
-    <row r="315" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B315" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C315">
         <v>168</v>
@@ -11291,12 +11293,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="316" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B316" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C316">
         <v>389</v>
@@ -11320,12 +11322,12 @@
         <v>217</v>
       </c>
     </row>
-    <row r="317" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B317" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C317">
         <v>159</v>
@@ -11349,12 +11351,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="318" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B318" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C318">
         <v>40</v>
@@ -11378,12 +11380,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="319" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B319" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C319">
         <v>41</v>
@@ -11407,12 +11409,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B320" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C320">
         <v>28</v>
@@ -11436,12 +11438,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="321" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B321" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C321">
         <v>77</v>
@@ -11465,12 +11467,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="322" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B322" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C322">
         <v>420</v>
@@ -11494,12 +11496,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="323" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B323" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C323">
         <v>452</v>
@@ -11523,12 +11525,12 @@
         <v>249</v>
       </c>
     </row>
-    <row r="324" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B324" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C324">
         <v>10</v>
@@ -11552,12 +11554,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B325" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C325">
         <v>47</v>
@@ -11581,12 +11583,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="326" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B326" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C326">
         <v>745</v>
@@ -11610,12 +11612,12 @@
         <v>386</v>
       </c>
     </row>
-    <row r="327" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B327" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C327">
         <v>296</v>
@@ -11639,12 +11641,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="328" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B328" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C328">
         <v>936</v>
@@ -11668,12 +11670,12 @@
         <v>531</v>
       </c>
     </row>
-    <row r="329" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B329" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C329">
         <v>2162</v>
@@ -11697,12 +11699,12 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="330" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B330" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C330">
         <v>1487</v>
@@ -11726,12 +11728,12 @@
         <v>868</v>
       </c>
     </row>
-    <row r="331" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B331" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C331">
         <v>5268</v>
@@ -11755,12 +11757,12 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="332" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B332" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C332">
         <v>27</v>
@@ -11784,12 +11786,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="333" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B333" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C333">
         <v>10</v>
@@ -11813,12 +11815,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="334" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B334" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C334">
         <v>34</v>
@@ -11842,12 +11844,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="335" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B335" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C335">
         <v>2419</v>
@@ -11871,12 +11873,12 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="336" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B336" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C336">
         <v>993</v>
@@ -11900,12 +11902,12 @@
         <v>594</v>
       </c>
     </row>
-    <row r="337" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B337" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C337">
         <v>255</v>
@@ -11929,12 +11931,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="338" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B338" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C338">
         <v>4844</v>
@@ -11958,12 +11960,12 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="339" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B339" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C339">
         <v>268</v>
@@ -11987,12 +11989,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="340" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B340" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C340">
         <v>5954</v>
@@ -12016,12 +12018,12 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="341" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B341" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C341">
         <v>620</v>
@@ -12045,12 +12047,12 @@
         <v>283</v>
       </c>
     </row>
-    <row r="342" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B342" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C342">
         <v>67</v>
@@ -12074,12 +12076,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B343" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C343">
         <v>97</v>
@@ -12103,12 +12105,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="344" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B344" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C344">
         <v>91</v>
@@ -12132,12 +12134,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="345" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B345" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C345">
         <v>167</v>
@@ -12161,12 +12163,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="346" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B346" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C346">
         <v>246</v>
@@ -12190,12 +12192,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="347" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B347" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C347">
         <v>107</v>
@@ -12219,12 +12221,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="348" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B348" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C348">
         <v>45</v>
@@ -12248,12 +12250,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="349" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B349" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C349">
         <v>125</v>
@@ -12277,12 +12279,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="350" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B350" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C350">
         <v>692</v>
@@ -12306,12 +12308,12 @@
         <v>407</v>
       </c>
     </row>
-    <row r="351" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B351" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C351">
         <v>2299</v>
@@ -12335,12 +12337,12 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="352" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B352" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C352">
         <v>3874</v>
@@ -12364,12 +12366,12 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="353" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B353" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C353">
         <v>85</v>
@@ -12393,12 +12395,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="354" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B354" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C354">
         <v>41</v>
@@ -12422,12 +12424,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="355" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B355" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C355">
         <v>495</v>
@@ -12451,12 +12453,12 @@
         <v>264</v>
       </c>
     </row>
-    <row r="356" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B356" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C356">
         <v>216</v>
@@ -12480,12 +12482,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="357" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B357" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C357">
         <v>319</v>
@@ -12509,12 +12511,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="358" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B358" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C358">
         <v>139</v>
@@ -12538,12 +12540,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="359" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B359" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C359">
         <v>97</v>
@@ -12567,12 +12569,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="360" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B360" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C360">
         <v>89</v>
@@ -12596,12 +12598,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="361" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B361" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C361">
         <v>4</v>
@@ -12625,12 +12627,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B362" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C362">
         <v>78</v>
@@ -12654,12 +12656,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="363" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B363" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C363">
         <v>60</v>
@@ -12683,12 +12685,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="364" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B364" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C364">
         <v>105</v>
@@ -12712,12 +12714,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="365" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B365" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C365">
         <v>132</v>
@@ -12741,12 +12743,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="366" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B366" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C366">
         <v>180</v>
@@ -12770,12 +12772,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="367" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B367" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C367">
         <v>172</v>
@@ -12799,12 +12801,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="368" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B368" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C368">
         <v>426</v>
@@ -12828,12 +12830,12 @@
         <v>300</v>
       </c>
     </row>
-    <row r="369" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B369" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C369">
         <v>9303</v>
@@ -12857,12 +12859,12 @@
         <v>4853</v>
       </c>
     </row>
-    <row r="370" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B370" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C370">
         <v>128</v>
@@ -12886,12 +12888,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="371" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B371" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C371">
         <v>83</v>
@@ -12915,12 +12917,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="372" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B372" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C372">
         <v>5032</v>
@@ -12944,12 +12946,12 @@
         <v>3360</v>
       </c>
     </row>
-    <row r="373" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B373" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C373">
         <v>42</v>
@@ -12973,12 +12975,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B374" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C374">
         <v>194</v>
@@ -13002,12 +13004,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="375" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B375" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C375">
         <v>189</v>
@@ -13031,12 +13033,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="376" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B376" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C376">
         <v>1396</v>
@@ -13060,12 +13062,12 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="377" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B377" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C377">
         <v>614</v>
@@ -13089,12 +13091,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="378" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B378" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C378">
         <v>256</v>
@@ -13118,12 +13120,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="379" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B379" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C379">
         <v>385</v>
@@ -13147,12 +13149,12 @@
         <v>316</v>
       </c>
     </row>
-    <row r="380" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B380" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C380">
         <v>28</v>
@@ -13176,12 +13178,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="381" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B381" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C381">
         <v>606</v>
@@ -13205,12 +13207,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="382" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B382" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C382">
         <v>11026</v>
@@ -13234,12 +13236,12 @@
         <v>4339</v>
       </c>
     </row>
-    <row r="383" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B383" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C383">
         <v>132</v>
@@ -13263,12 +13265,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="384" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B384" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C384">
         <v>90</v>
@@ -13292,12 +13294,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="385" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B385" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C385">
         <v>520</v>
@@ -13321,12 +13323,12 @@
         <v>404</v>
       </c>
     </row>
-    <row r="386" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B386" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C386">
         <v>76</v>
@@ -13350,12 +13352,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="387" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B387" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C387">
         <v>354</v>
@@ -13379,12 +13381,12 @@
         <v>254</v>
       </c>
     </row>
-    <row r="388" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B388" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C388">
         <v>442</v>
@@ -13408,12 +13410,12 @@
         <v>203</v>
       </c>
     </row>
-    <row r="389" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B389" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C389">
         <v>988</v>
@@ -13437,12 +13439,12 @@
         <v>262</v>
       </c>
     </row>
-    <row r="390" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B390" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C390">
         <v>651</v>
@@ -13466,12 +13468,12 @@
         <v>505</v>
       </c>
     </row>
-    <row r="391" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B391" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C391">
         <v>79</v>
@@ -13495,12 +13497,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="392" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B392" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C392">
         <v>244</v>
@@ -13524,12 +13526,12 @@
         <v>197</v>
       </c>
     </row>
-    <row r="393" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B393" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C393">
         <v>274</v>
@@ -13553,12 +13555,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="394" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B394" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C394">
         <v>112</v>
@@ -13582,12 +13584,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="395" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B395" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C395">
         <v>113</v>
@@ -13611,12 +13613,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="396" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B396" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C396">
         <v>362</v>
@@ -13640,12 +13642,12 @@
         <v>244</v>
       </c>
     </row>
-    <row r="397" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B397" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C397">
         <v>173</v>
@@ -13669,12 +13671,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="398" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B398" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C398">
         <v>131</v>
@@ -13698,12 +13700,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="399" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B399" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C399">
         <v>174</v>
@@ -13727,12 +13729,12 @@
         <v>136</v>
       </c>
     </row>
-    <row r="400" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B400" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C400">
         <v>71</v>
@@ -13756,12 +13758,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="401" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B401" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C401">
         <v>129</v>
@@ -13785,12 +13787,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="402" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B402" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C402">
         <v>3839</v>
@@ -13814,12 +13816,12 @@
         <v>2563</v>
       </c>
     </row>
-    <row r="403" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B403" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C403">
         <v>133</v>
@@ -13843,12 +13845,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="404" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B404" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C404">
         <v>2890</v>
@@ -13872,12 +13874,12 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="405" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B405" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C405">
         <v>1396</v>
@@ -13901,12 +13903,12 @@
         <v>790</v>
       </c>
     </row>
-    <row r="406" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B406" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C406">
         <v>879</v>
@@ -13930,12 +13932,12 @@
         <v>523</v>
       </c>
     </row>
-    <row r="407" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B407" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C407">
         <v>121</v>
@@ -13959,12 +13961,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="408" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B408" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C408">
         <v>709</v>
@@ -13988,12 +13990,12 @@
         <v>397</v>
       </c>
     </row>
-    <row r="409" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B409" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C409">
         <v>248</v>
@@ -14017,12 +14019,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="410" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B410" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C410">
         <v>40</v>
@@ -14046,12 +14048,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="411" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B411" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C411">
         <v>157</v>
@@ -14075,12 +14077,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="412" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B412" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C412">
         <v>291</v>
@@ -14104,12 +14106,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="413" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B413" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C413">
         <v>424</v>
@@ -14133,12 +14135,12 @@
         <v>295</v>
       </c>
     </row>
-    <row r="414" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B414" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C414">
         <v>677</v>
@@ -14162,12 +14164,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="415" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B415" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C415">
         <v>928</v>
@@ -14191,12 +14193,12 @@
         <v>743</v>
       </c>
     </row>
-    <row r="416" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B416" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C416">
         <v>888</v>
@@ -14220,12 +14222,12 @@
         <v>659</v>
       </c>
     </row>
-    <row r="417" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B417" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C417">
         <v>3939</v>
@@ -14249,12 +14251,12 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="418" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B418" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C418">
         <v>436</v>
@@ -14278,12 +14280,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="419" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B419" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C419">
         <v>2876</v>
@@ -14307,12 +14309,12 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="420" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B420" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C420">
         <v>69</v>
@@ -14336,12 +14338,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="421" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B421" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C421">
         <v>14</v>
@@ -14365,12 +14367,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="422" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B422" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C422">
         <v>2179</v>
@@ -14394,12 +14396,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="423" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B423" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C423">
         <v>944</v>
@@ -14423,12 +14425,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="424" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B424" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C424">
         <v>153</v>
@@ -14452,12 +14454,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="425" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B425" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C425">
         <v>312</v>
@@ -14481,12 +14483,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="426" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B426" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C426">
         <v>126</v>
@@ -14510,12 +14512,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="427" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B427" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C427">
         <v>2105</v>
@@ -14539,12 +14541,12 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="428" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B428" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C428">
         <v>185</v>
@@ -14568,12 +14570,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="429" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B429" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C429">
         <v>52</v>
@@ -14597,12 +14599,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="430" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B430" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C430">
         <v>272</v>
@@ -14626,12 +14628,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="431" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B431" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C431">
         <v>54</v>
@@ -14655,12 +14657,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="432" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B432" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C432">
         <v>104</v>
@@ -14684,12 +14686,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="433" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B433" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C433">
         <v>52</v>
@@ -14713,12 +14715,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="434" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B434" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C434">
         <v>127</v>
@@ -14742,12 +14744,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="435" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B435" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C435">
         <v>917</v>
@@ -14771,12 +14773,12 @@
         <v>741</v>
       </c>
     </row>
-    <row r="436" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B436" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C436">
         <v>27</v>
@@ -14800,12 +14802,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="437" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B437" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C437">
         <v>470</v>
@@ -14829,12 +14831,12 @@
         <v>339</v>
       </c>
     </row>
-    <row r="438" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B438" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C438">
         <v>177</v>
@@ -14858,12 +14860,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="439" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B439" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C439">
         <v>262</v>
@@ -14887,12 +14889,12 @@
         <v>214</v>
       </c>
     </row>
-    <row r="440" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B440" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C440">
         <v>1408</v>
@@ -14916,12 +14918,12 @@
         <v>860</v>
       </c>
     </row>
-    <row r="441" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B441" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C441">
         <v>524</v>
@@ -14945,12 +14947,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="442" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B442" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C442">
         <v>252</v>
@@ -14974,12 +14976,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="443" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B443" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C443">
         <v>59</v>
@@ -15003,12 +15005,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="444" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B444" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C444">
         <v>297</v>
@@ -15032,12 +15034,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="445" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B445" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C445">
         <v>670</v>
@@ -15061,12 +15063,12 @@
         <v>531</v>
       </c>
     </row>
-    <row r="446" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B446" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C446">
         <v>31</v>
@@ -15090,12 +15092,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="447" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B447" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C447">
         <v>142</v>
@@ -15119,12 +15121,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="448" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B448" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C448">
         <v>294</v>
@@ -15148,12 +15150,12 @@
         <v>246</v>
       </c>
     </row>
-    <row r="449" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B449" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C449">
         <v>197</v>
@@ -15177,12 +15179,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="450" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B450" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C450">
         <v>1690</v>
@@ -15206,12 +15208,12 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="451" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B451" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C451">
         <v>118</v>
@@ -15235,12 +15237,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="452" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B452" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C452">
         <v>358</v>
@@ -15264,12 +15266,12 @@
         <v>186</v>
       </c>
     </row>
-    <row r="453" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B453" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C453">
         <v>652</v>
@@ -15293,12 +15295,12 @@
         <v>399</v>
       </c>
     </row>
-    <row r="454" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B454" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C454">
         <v>151</v>
@@ -15322,12 +15324,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="455" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B455" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C455">
         <v>707</v>
@@ -15351,12 +15353,12 @@
         <v>601</v>
       </c>
     </row>
-    <row r="456" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B456" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C456">
         <v>213</v>
@@ -15380,12 +15382,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="457" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B457" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C457">
         <v>125</v>
@@ -15409,12 +15411,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="458" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B458" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C458">
         <v>19</v>
@@ -15438,12 +15440,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="459" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B459" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C459">
         <v>204</v>
@@ -15467,12 +15469,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="460" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B460" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C460">
         <v>244</v>
@@ -15496,12 +15498,12 @@
         <v>186</v>
       </c>
     </row>
-    <row r="461" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B461" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C461">
         <v>111</v>
@@ -15525,12 +15527,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="462" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B462" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C462">
         <v>632</v>
@@ -15554,12 +15556,12 @@
         <v>414</v>
       </c>
     </row>
-    <row r="463" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B463" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C463">
         <v>63</v>
@@ -15583,12 +15585,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="464" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B464" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C464">
         <v>29</v>
@@ -15612,12 +15614,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="465" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B465" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C465">
         <v>46</v>
@@ -15641,12 +15643,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="466" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B466" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C466">
         <v>847</v>
@@ -15670,12 +15672,12 @@
         <v>671</v>
       </c>
     </row>
-    <row r="467" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B467" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C467">
         <v>39</v>
@@ -15699,12 +15701,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="468" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B468" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C468">
         <v>2378</v>
@@ -15728,12 +15730,12 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="469" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B469" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C469">
         <v>1140</v>
@@ -15757,12 +15759,12 @@
         <v>688</v>
       </c>
     </row>
-    <row r="470" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B470" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C470">
         <v>499</v>
@@ -15786,12 +15788,12 @@
         <v>441</v>
       </c>
     </row>
-    <row r="471" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B471" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C471">
         <v>196</v>
@@ -15815,12 +15817,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="472" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B472" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C472">
         <v>98</v>
@@ -15844,12 +15846,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="473" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B473" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C473">
         <v>22</v>
@@ -15873,12 +15875,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="474" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B474" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C474">
         <v>109</v>
@@ -15902,12 +15904,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B475" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C475">
         <v>42</v>
@@ -15931,12 +15933,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="476" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B476" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C476">
         <v>165</v>
@@ -15960,12 +15962,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="477" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B477" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C477">
         <v>47</v>
@@ -15989,12 +15991,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="478" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B478" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C478">
         <v>25</v>
@@ -16018,12 +16020,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="479" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B479" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C479">
         <v>73</v>
@@ -16047,12 +16049,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="480" spans="1:9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B480" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C480">
         <v>262</v>
@@ -16076,12 +16078,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="481" spans="1:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B481" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C481">
         <v>502</v>
@@ -16105,12 +16107,12 @@
         <v>373</v>
       </c>
     </row>
-    <row r="482" spans="1:14" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B482" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C482">
         <v>191</v>
@@ -16134,28 +16136,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A483" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B483" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C483"/>
-      <c r="D483"/>
-      <c r="E483"/>
-      <c r="F483"/>
-      <c r="G483"/>
-      <c r="H483"/>
-      <c r="I483"/>
-      <c r="J483" s="2"/>
-      <c r="K483" s="2"/>
-      <c r="L483" s="2"/>
-      <c r="M483" s="2"/>
-      <c r="N483"/>
-    </row>
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:I482" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:I483" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="Papilionoidea"/>
@@ -16168,81 +16151,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fd5dee7c-ba60-42c5-972c-0266fa4c6388">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="159907c2-825f-4798-be3c-cace777c1bf6" xsi:nil="true"/>
-    <_dlc_DocId xmlns="159907c2-825f-4798-be3c-cace777c1bf6">EXME54VS2YUU-1818840572-15979</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="159907c2-825f-4798-be3c-cace777c1bf6">
-      <Url>https://universityoflatvia387.sharepoint.com/sites/HiQBioDiv/_layouts/15/DocIdRedir.aspx?ID=EXME54VS2YUU-1818840572-15979</Url>
-      <Description>EXME54VS2YUU-1818840572-15979</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100147FB57513909B4BA2EA8B3E2CB0A604" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4d01b0cde4e466c4988ee76d55e29fc9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="159907c2-825f-4798-be3c-cace777c1bf6" xmlns:ns3="fd5dee7c-ba60-42c5-972c-0266fa4c6388" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="555f493e4267aa03dcad174e56e1dacc" ns2:_="" ns3:_="">
     <xsd:import namespace="159907c2-825f-4798-be3c-cace777c1bf6"/>
@@ -16468,34 +16376,82 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44E9BD31-6645-4B98-9051-45A80DD204A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fd5dee7c-ba60-42c5-972c-0266fa4c6388">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="159907c2-825f-4798-be3c-cace777c1bf6" xsi:nil="true"/>
+    <_dlc_DocId xmlns="159907c2-825f-4798-be3c-cace777c1bf6">EXME54VS2YUU-1818840572-15979</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="159907c2-825f-4798-be3c-cace777c1bf6">
+      <Url>https://universityoflatvia387.sharepoint.com/sites/HiQBioDiv/_layouts/15/DocIdRedir.aspx?ID=EXME54VS2YUU-1818840572-15979</Url>
+      <Description>EXME54VS2YUU-1818840572-15979</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA2A3BDA-8A7D-4EEE-AFCF-72DBE4A88DE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A0CBA5-068E-440E-9C54-AD8F66C32F7A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fd5dee7c-ba60-42c5-972c-0266fa4c6388"/>
-    <ds:schemaRef ds:uri="159907c2-825f-4798-be3c-cace777c1bf6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AA545E5-31B2-4840-A2D5-6C612417FD79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16512,4 +16468,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A0CBA5-068E-440E-9C54-AD8F66C32F7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fd5dee7c-ba60-42c5-972c-0266fa4c6388"/>
+    <ds:schemaRef ds:uri="159907c2-825f-4798-be3c-cace777c1bf6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA2A3BDA-8A7D-4EEE-AFCF-72DBE4A88DE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44E9BD31-6645-4B98-9051-45A80DD204A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>